--- a/sales report.xlsx
+++ b/sales report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\Excel Practice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\Excel_Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C23698D-573D-41F2-9C3C-8AC33446899C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2777B663-AF23-4942-8D83-3807B23A618C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{EE8956C5-3C9B-4156-9E02-20B0B3A2E2D3}"/>
   </bookViews>
@@ -18,10 +18,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sales Report'!$A$1:$K$172</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="1">'Sales Report'!$T$7:$U$8</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="1">'Sales Report'!$U$12:$AE$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="63">
   <si>
     <t>NV</t>
   </si>
@@ -222,6 +224,15 @@
   <si>
     <t>Pivot table</t>
   </si>
+  <si>
+    <t>&gt;100</t>
+  </si>
+  <si>
+    <t>Advance filter criteria range</t>
+  </si>
+  <si>
+    <t>Advance filter result</t>
+  </si>
 </sst>
 </file>
 
@@ -233,7 +244,7 @@
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,8 +282,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +322,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -319,7 +344,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -354,6 +379,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{21ADE797-B38F-4273-B8D1-28699080A9AD}"/>
@@ -1486,8 +1527,8 @@
       <xdr:rowOff>119865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>222607</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173790</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>162674</xdr:rowOff>
     </xdr:to>
@@ -1504,8 +1545,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10205663" y="1172966"/>
-          <a:ext cx="3707259" cy="2208944"/>
+          <a:off x="10203861" y="1175970"/>
+          <a:ext cx="4768771" cy="3291336"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1549,9 +1590,9 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-IN" sz="2000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1563,7 +1604,7 @@
             <a:t>Topics covered in this</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-IN" sz="2000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1598,6 +1639,20 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>text to columns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>advance filter</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1709,22 +1764,45 @@
         <a:p>
           <a:endParaRPr lang="en-IN" sz="1600"/>
         </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1600"/>
+            <a:t>Absolute</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1600" baseline="0"/>
+            <a:t> and relative reference: press</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1600" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> f4 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1600" baseline="0"/>
+            <a:t>for relative ref.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1600"/>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>321066</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>105309</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>27152</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>61766</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>273977</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1155720</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>25685</xdr:rowOff>
+      <xdr:rowOff>178085</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4063,7 +4141,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC0B2B3E-4836-4D92-A258-836F8017C8DA}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC0B2B3E-4836-4D92-A258-836F8017C8DA}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
   <location ref="A3:P16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -4602,7 +4680,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{808463B6-A058-4FEE-88CF-A3D535845ABD}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{808463B6-A058-4FEE-88CF-A3D535845ABD}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="P21:Q26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -5696,7 +5774,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q178"/>
+  <dimension ref="A1:AE178"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -5711,10 +5789,19 @@
     <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.77734375" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" customWidth="1"/>
+    <col min="22" max="22" width="27.109375" customWidth="1"/>
+    <col min="23" max="23" width="18.21875" customWidth="1"/>
+    <col min="24" max="24" width="18.109375" customWidth="1"/>
+    <col min="25" max="25" width="15.33203125" customWidth="1"/>
+    <col min="26" max="27" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.5546875" customWidth="1"/>
+    <col min="29" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="7" customFormat="1" ht="82.8" customHeight="1">
+    <row r="1" spans="1:31" s="7" customFormat="1" ht="82.8" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>46</v>
       </c>
@@ -5749,32 +5836,32 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
+    <row r="2" spans="1:31" ht="15.6">
       <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="4">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C2" s="2">
-        <v>9822</v>
+        <v>8722</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3">
-        <v>58.3</v>
+        <v>344</v>
       </c>
       <c r="F2" s="3">
-        <v>98.4</v>
+        <v>502</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" ref="G2:G33" si="0">F2-E2</f>
-        <v>40.100000000000009</v>
+        <f>F2-E2</f>
+        <v>158</v>
       </c>
       <c r="H2" s="3">
-        <f t="shared" ref="H2:H33" si="1">IF(F2&gt;50, G2*0.2, G2*0.1)</f>
-        <v>8.0200000000000014</v>
+        <f>IF(F2&gt;50, G2*0.2, G2*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>7</v>
@@ -5783,72 +5870,72 @@
         <v>6</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="15.6">
       <c r="A3" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B3" s="4">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="C3" s="2">
-        <v>2877</v>
+        <v>8722</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3">
-        <v>11.4</v>
+        <v>344</v>
       </c>
       <c r="F3" s="3">
-        <v>16.3</v>
+        <v>502</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F3-E3</f>
+        <v>158</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F3&gt;50, G3*0.2, G3*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6">
+    <row r="4" spans="1:31" ht="15.6">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="4">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="C4" s="2">
-        <v>2499</v>
+        <v>8722</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3">
-        <v>6.2</v>
+        <v>344</v>
       </c>
       <c r="F4" s="3">
-        <v>9.1999999999999993</v>
+        <v>502</v>
       </c>
       <c r="G4" s="3">
-        <f t="shared" si="0"/>
-        <v>2.9999999999999991</v>
+        <f>F4-E4</f>
+        <v>158</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F4&gt;50, G4*0.2, G4*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
@@ -5857,15 +5944,15 @@
         <v>6</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="15.6">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="4">
-        <v>1004</v>
+        <v>1048</v>
       </c>
       <c r="C5" s="2">
         <v>8722</v>
@@ -5880,11 +5967,11 @@
         <v>502</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" si="0"/>
+        <f>F5-E5</f>
         <v>158</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(F5&gt;50, G5*0.2, G5*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -5897,297 +5984,350 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6">
+    <row r="6" spans="1:31" ht="18">
       <c r="A6" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4">
-        <v>1005</v>
+        <v>1115</v>
       </c>
       <c r="C6" s="2">
-        <v>1109</v>
+        <v>8722</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3">
-        <v>3</v>
+        <v>344</v>
       </c>
       <c r="F6" s="3">
-        <v>8</v>
+        <v>502</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>F6-E6</f>
+        <v>158</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IF(F6&gt;50, G6*0.2, G6*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6">
+      <c r="T6" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="U6" s="20"/>
+    </row>
+    <row r="7" spans="1:31" ht="31.2">
       <c r="A7" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>1006</v>
+        <v>1127</v>
       </c>
       <c r="C7" s="2">
-        <v>9822</v>
+        <v>8722</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="3">
-        <v>58.3</v>
+        <v>344</v>
       </c>
       <c r="F7" s="3">
-        <v>98.4</v>
+        <v>502</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="0"/>
-        <v>40.100000000000009</v>
+        <f>F7-E7</f>
+        <v>158</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="1"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F7&gt;50, G7*0.2, G7*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.6">
+      <c r="T7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" ht="15.6">
       <c r="A8" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4">
-        <v>1007</v>
+        <v>1135</v>
       </c>
       <c r="C8" s="2">
-        <v>1109</v>
+        <v>8722</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3">
-        <v>3</v>
+        <v>344</v>
       </c>
       <c r="F8" s="3">
+        <v>502</v>
+      </c>
+      <c r="G8" s="3">
+        <f>F8-E8</f>
+        <v>158</v>
+      </c>
+      <c r="H8" s="3">
+        <f>IF(F8&gt;50, G8*0.2, G8*0.1)</f>
+        <v>31.6</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6"/>
+      <c r="T8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="15.6">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1138</v>
+      </c>
+      <c r="C9" s="2">
+        <v>8722</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3">
+        <v>344</v>
+      </c>
+      <c r="F9" s="3">
+        <v>502</v>
+      </c>
+      <c r="G9" s="3">
+        <f>F9-E9</f>
+        <v>158</v>
+      </c>
+      <c r="H9" s="3">
+        <f>IF(F9&gt;50, G9*0.2, G9*0.1)</f>
+        <v>31.6</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.6">
-      <c r="A9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1008</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2877</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>11.4</v>
-      </c>
-      <c r="F9" s="3">
-        <v>16.3</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="O9" s="6"/>
     </row>
-    <row r="10" spans="1:15" ht="15.6">
+    <row r="10" spans="1:31" ht="15.6">
       <c r="A10" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B10" s="4">
-        <v>1009</v>
+        <v>1149</v>
       </c>
       <c r="C10" s="2">
-        <v>1109</v>
+        <v>8722</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
+        <v>344</v>
       </c>
       <c r="F10" s="3">
-        <v>8</v>
+        <v>502</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>F10-E10</f>
+        <v>158</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IF(F10&gt;50, G10*0.2, G10*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="1:15" ht="15.6">
+    <row r="11" spans="1:31" ht="18">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B11" s="4">
-        <v>1010</v>
+        <v>1158</v>
       </c>
       <c r="C11" s="2">
-        <v>2877</v>
+        <v>8722</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E11" s="3">
-        <v>11.4</v>
+        <v>344</v>
       </c>
       <c r="F11" s="3">
-        <v>16.3</v>
+        <v>502</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F11-E11</f>
+        <v>158</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F11&gt;50, G11*0.2, G11*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.6">
+      <c r="U11" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="V11" s="27"/>
+    </row>
+    <row r="12" spans="1:31" ht="78">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4">
-        <v>1011</v>
+        <v>1042</v>
       </c>
       <c r="C12" s="2">
-        <v>2877</v>
+        <v>8722</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3">
-        <v>11.4</v>
+        <v>344</v>
       </c>
       <c r="F12" s="3">
-        <v>16.3</v>
+        <v>502</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F12-E12</f>
+        <v>158</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F12&gt;50, G12*0.2, G12*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.6">
+      <c r="U12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="V12" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="W12" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="X12" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y12" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z12" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC12" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD12" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE12" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="15.6">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B13" s="4">
-        <v>1012</v>
+        <v>1122</v>
       </c>
       <c r="C13" s="2">
-        <v>4421</v>
+        <v>8722</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E13" s="3">
-        <v>45</v>
+        <v>344</v>
       </c>
       <c r="F13" s="3">
-        <v>87</v>
+        <v>502</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <f>F13-E13</f>
+        <v>158</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="1"/>
-        <v>8.4</v>
+        <f>IF(F13&gt;50, G13*0.2, G13*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>10</v>
@@ -6196,53 +6336,119 @@
         <v>9</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O13" s="6"/>
+      <c r="U13" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="V13" s="24">
+        <v>1017</v>
+      </c>
+      <c r="W13" s="25">
+        <v>2242</v>
+      </c>
+      <c r="X13" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y13" s="26">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="26">
+        <v>124</v>
+      </c>
+      <c r="AA13" s="26">
+        <v>64</v>
+      </c>
+      <c r="AB13" s="26">
+        <v>12.8</v>
+      </c>
+      <c r="AC13" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.6">
+    </row>
+    <row r="14" spans="1:31" ht="15.6">
       <c r="A14" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4">
-        <v>1013</v>
+        <v>1153</v>
       </c>
       <c r="C14" s="2">
-        <v>9212</v>
+        <v>8722</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E14" s="3">
-        <v>4</v>
+        <v>344</v>
       </c>
       <c r="F14" s="3">
-        <v>7</v>
+        <v>502</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>F14-E14</f>
+        <v>158</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F14&gt;50, G14*0.2, G14*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6">
+        <v>16</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="24">
+        <v>1102</v>
+      </c>
+      <c r="W14" s="25">
+        <v>2242</v>
+      </c>
+      <c r="X14" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y14" s="26">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="26">
+        <v>124</v>
+      </c>
+      <c r="AA14" s="26">
+        <v>64</v>
+      </c>
+      <c r="AB14" s="26">
+        <v>12.8</v>
+      </c>
+      <c r="AC14" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="15.6">
       <c r="A15" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>1014</v>
+        <v>1166</v>
       </c>
       <c r="C15" s="2">
         <v>8722</v>
@@ -6257,243 +6463,397 @@
         <v>502</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="0"/>
+        <f>F15-E15</f>
         <v>158</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(F15&gt;50, G15*0.2, G15*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U15" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="V15" s="24">
+        <v>1109</v>
+      </c>
+      <c r="W15" s="25">
+        <v>8722</v>
+      </c>
+      <c r="X15" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y15" s="26">
+        <v>344</v>
+      </c>
+      <c r="Z15" s="26">
+        <v>502</v>
+      </c>
+      <c r="AA15" s="26">
+        <v>158</v>
+      </c>
+      <c r="AB15" s="26">
+        <v>31.6</v>
+      </c>
+      <c r="AC15" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD15" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6">
+    <row r="16" spans="1:31" ht="15.6">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B16" s="4">
-        <v>1015</v>
+        <v>1169</v>
       </c>
       <c r="C16" s="2">
-        <v>2877</v>
+        <v>8722</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E16" s="3">
-        <v>11.4</v>
+        <v>344</v>
       </c>
       <c r="F16" s="3">
-        <v>16.3</v>
+        <v>502</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F16-E16</f>
+        <v>158</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F16&gt;50, G16*0.2, G16*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U16" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="V16" s="24">
+        <v>1114</v>
+      </c>
+      <c r="W16" s="25">
+        <v>2242</v>
+      </c>
+      <c r="X16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="26">
+        <v>60</v>
+      </c>
+      <c r="Z16" s="26">
+        <v>124</v>
+      </c>
+      <c r="AA16" s="26">
+        <v>64</v>
+      </c>
+      <c r="AB16" s="26">
+        <v>12.8</v>
+      </c>
+      <c r="AC16" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" ht="15.6">
+      <c r="A17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1045</v>
+      </c>
+      <c r="C17" s="2">
+        <v>8722</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3">
+        <v>344</v>
+      </c>
+      <c r="F17" s="3">
+        <v>502</v>
+      </c>
+      <c r="G17" s="3">
+        <f>F17-E17</f>
+        <v>158</v>
+      </c>
+      <c r="H17" s="3">
+        <f>IF(F17&gt;50, G17*0.2, G17*0.1)</f>
+        <v>31.6</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.6">
-      <c r="A17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="4">
-        <v>1049</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2499</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G17" s="3">
-        <f t="shared" si="0"/>
-        <v>2.9999999999999991</v>
-      </c>
-      <c r="H17" s="3">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999993</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="15.6">
+      <c r="U17" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="V17" s="24">
+        <v>1142</v>
+      </c>
+      <c r="W17" s="25">
+        <v>2242</v>
+      </c>
+      <c r="X17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="26">
+        <v>60</v>
+      </c>
+      <c r="Z17" s="26">
+        <v>124</v>
+      </c>
+      <c r="AA17" s="26">
+        <v>64</v>
+      </c>
+      <c r="AB17" s="26">
+        <v>12.8</v>
+      </c>
+      <c r="AC17" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD17" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" ht="15.6">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4">
-        <v>1017</v>
+        <v>1110</v>
       </c>
       <c r="C18" s="2">
+        <v>8722</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3">
+        <v>344</v>
+      </c>
+      <c r="F18" s="3">
+        <v>502</v>
+      </c>
+      <c r="G18" s="3">
+        <f>F18-E18</f>
+        <v>158</v>
+      </c>
+      <c r="H18" s="3">
+        <f>IF(F18&gt;50, G18*0.2, G18*0.1)</f>
+        <v>31.6</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U18" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="V18" s="24">
+        <v>1151</v>
+      </c>
+      <c r="W18" s="25">
         <v>2242</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="X18" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="3">
+      <c r="Y18" s="26">
         <v>60</v>
       </c>
-      <c r="F18" s="3">
+      <c r="Z18" s="26">
         <v>124</v>
       </c>
-      <c r="G18" s="3">
-        <f t="shared" si="0"/>
+      <c r="AA18" s="26">
         <v>64</v>
       </c>
-      <c r="H18" s="3">
-        <f t="shared" si="1"/>
+      <c r="AB18" s="26">
         <v>12.8</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="AC18" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="AD18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="AE18" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" ht="15.6">
+      <c r="A19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1117</v>
+      </c>
+      <c r="C19" s="2">
+        <v>8722</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3">
+        <v>344</v>
+      </c>
+      <c r="F19" s="3">
+        <v>502</v>
+      </c>
+      <c r="G19" s="3">
+        <f>F19-E19</f>
+        <v>158</v>
+      </c>
+      <c r="H19" s="3">
+        <f>IF(F19&gt;50, G19*0.2, G19*0.1)</f>
+        <v>31.6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="15.6">
-      <c r="A19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="4">
-        <v>1018</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1109</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>3</v>
-      </c>
-      <c r="F19" s="3">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H19" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="P19" s="19" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" ht="15.6">
+      <c r="U19" s="5"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+    </row>
+    <row r="20" spans="1:31" ht="15.6">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
-        <v>1062</v>
+        <v>1146</v>
       </c>
       <c r="C20" s="2">
-        <v>2499</v>
+        <v>8722</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E20" s="3">
-        <v>6.2</v>
+        <v>344</v>
       </c>
       <c r="F20" s="3">
-        <v>9.1999999999999993</v>
+        <v>502</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="0"/>
-        <v>2.9999999999999991</v>
+        <f>F20-E20</f>
+        <v>158</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F20&gt;50, G20*0.2, G20*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="15.6">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+    </row>
+    <row r="21" spans="1:31" ht="15.6">
       <c r="A21" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4">
-        <v>1087</v>
+        <v>1109</v>
       </c>
       <c r="C21" s="2">
-        <v>2499</v>
+        <v>8722</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E21" s="3">
-        <v>6.2</v>
+        <v>344</v>
       </c>
       <c r="F21" s="3">
-        <v>9.1999999999999993</v>
+        <v>502</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="0"/>
-        <v>2.9999999999999991</v>
+        <f>F21-E21</f>
+        <v>158</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F21&gt;50, G21*0.2, G21*0.1)</f>
+        <v>31.6</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>5</v>
@@ -6504,42 +6864,53 @@
       <c r="Q21" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" ht="15.6">
+      <c r="U21" s="5"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+    </row>
+    <row r="22" spans="1:31" ht="15.6">
       <c r="A22" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="4">
-        <v>1021</v>
+        <v>1053</v>
       </c>
       <c r="C22" s="2">
-        <v>1109</v>
+        <v>2242</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E22" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F22" s="3">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="0"/>
+        <f>F22-E22</f>
+        <v>64</v>
+      </c>
+      <c r="H22" s="3">
+        <f>IF(F22&gt;50, G22*0.2, G22*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>6</v>
@@ -6547,39 +6918,50 @@
       <c r="Q22" s="1">
         <v>6003.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" ht="15.6">
+      <c r="U22" s="5"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+    </row>
+    <row r="23" spans="1:31" ht="15.6">
       <c r="A23" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B23" s="4">
-        <v>1022</v>
+        <v>1119</v>
       </c>
       <c r="C23" s="2">
-        <v>2877</v>
+        <v>2242</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E23" s="3">
-        <v>11.4</v>
+        <v>60</v>
       </c>
       <c r="F23" s="3">
-        <v>16.3</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F23-E23</f>
+        <v>64</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F23&gt;50, G23*0.2, G23*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>8</v>
@@ -6590,42 +6972,53 @@
       <c r="Q23" s="1">
         <v>2410.7000000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" ht="15.6">
+      <c r="U23" s="5"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+    </row>
+    <row r="24" spans="1:31" ht="15.6">
       <c r="A24" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="4">
-        <v>1023</v>
+        <v>1043</v>
       </c>
       <c r="C24" s="2">
-        <v>1109</v>
+        <v>2242</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E24" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F24" s="3">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="0"/>
+        <f>F24-E24</f>
+        <v>64</v>
+      </c>
+      <c r="H24" s="3">
+        <f>IF(F24&gt;50, G24*0.2, G24*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H24" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>18</v>
@@ -6633,42 +7026,53 @@
       <c r="Q24" s="1">
         <v>3035.3</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" ht="15.6">
+      <c r="U24" s="5"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+    </row>
+    <row r="25" spans="1:31" ht="15.6">
       <c r="A25" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4">
-        <v>1024</v>
+        <v>1059</v>
       </c>
       <c r="C25" s="2">
-        <v>9212</v>
+        <v>2242</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E25" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F25" s="3">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>F25-E25</f>
+        <v>64</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F25&gt;50, G25*0.2, G25*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P25" s="11" t="s">
         <v>9</v>
@@ -6676,42 +7080,53 @@
       <c r="Q25" s="1">
         <v>5661.0999999999985</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" ht="15.6">
+      <c r="U25" s="5"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+    </row>
+    <row r="26" spans="1:31" ht="15.6">
       <c r="A26" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4">
-        <v>1025</v>
+        <v>1120</v>
       </c>
       <c r="C26" s="2">
-        <v>2877</v>
+        <v>2242</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E26" s="3">
-        <v>11.4</v>
+        <v>60</v>
       </c>
       <c r="F26" s="3">
-        <v>16.3</v>
+        <v>124</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F26-E26</f>
+        <v>64</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F26&gt;50, G26*0.2, G26*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" s="11" t="s">
         <v>51</v>
@@ -6719,292 +7134,369 @@
       <c r="Q26" s="1">
         <v>17110.599999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" ht="15.6">
+      <c r="U26" s="5"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+    </row>
+    <row r="27" spans="1:31" ht="15.6">
       <c r="A27" s="5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B27" s="4">
-        <v>1026</v>
+        <v>1125</v>
       </c>
       <c r="C27" s="2">
-        <v>6119</v>
+        <v>2242</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E27" s="3">
+        <v>60</v>
+      </c>
+      <c r="F27" s="3">
+        <v>124</v>
+      </c>
+      <c r="G27" s="3">
+        <f>F27-E27</f>
+        <v>64</v>
+      </c>
+      <c r="H27" s="3">
+        <f>IF(F27&gt;50, G27*0.2, G27*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="3">
+      <c r="K27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="5"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+    </row>
+    <row r="28" spans="1:31" ht="15.6">
+      <c r="A28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="4">
+        <v>1136</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2242</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="3">
-        <f t="shared" si="0"/>
+      <c r="E28" s="3">
+        <v>60</v>
+      </c>
+      <c r="F28" s="3">
+        <v>124</v>
+      </c>
+      <c r="G28" s="3">
+        <f>F28-E28</f>
+        <v>64</v>
+      </c>
+      <c r="H28" s="3">
+        <f>IF(F28&gt;50, G28*0.2, G28*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U28" s="5"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+    </row>
+    <row r="29" spans="1:31" ht="15.6">
+      <c r="A29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4">
+        <v>1150</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2242</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="3">
+        <v>60</v>
+      </c>
+      <c r="F29" s="3">
+        <v>124</v>
+      </c>
+      <c r="G29" s="3">
+        <f>F29-E29</f>
+        <v>64</v>
+      </c>
+      <c r="H29" s="3">
+        <f>IF(F29&gt;50, G29*0.2, G29*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="5"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+    </row>
+    <row r="30" spans="1:31" ht="15.6">
+      <c r="A30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="4">
+        <v>1156</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2242</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="3">
+        <v>60</v>
+      </c>
+      <c r="F30" s="3">
+        <v>124</v>
+      </c>
+      <c r="G30" s="3">
+        <f>F30-E30</f>
+        <v>64</v>
+      </c>
+      <c r="H30" s="3">
+        <f>IF(F30&gt;50, G30*0.2, G30*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I27" s="2" t="s">
+      <c r="U30" s="5"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+    </row>
+    <row r="31" spans="1:31" ht="15.6">
+      <c r="A31" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1167</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2242</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="3">
+        <v>60</v>
+      </c>
+      <c r="F31" s="3">
+        <v>124</v>
+      </c>
+      <c r="G31" s="3">
+        <f>F31-E31</f>
+        <v>64</v>
+      </c>
+      <c r="H31" s="3">
+        <f>IF(F31&gt;50, G31*0.2, G31*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U31" s="5"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+    </row>
+    <row r="32" spans="1:31" ht="15.6">
+      <c r="A32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4">
+        <v>1144</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2242</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3">
+        <v>60</v>
+      </c>
+      <c r="F32" s="3">
+        <v>124</v>
+      </c>
+      <c r="G32" s="3">
+        <f>F32-E32</f>
+        <v>64</v>
+      </c>
+      <c r="H32" s="3">
+        <f>IF(F32&gt;50, G32*0.2, G32*0.1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="15.6">
-      <c r="A28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="4">
-        <v>1027</v>
-      </c>
-      <c r="C28" s="2">
-        <v>6119</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3">
-        <v>14</v>
-      </c>
-      <c r="G28" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H28" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="15.6">
-      <c r="A29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="4">
-        <v>1028</v>
-      </c>
-      <c r="C29" s="2">
-        <v>8722</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="3">
-        <v>344</v>
-      </c>
-      <c r="F29" s="3">
-        <v>502</v>
-      </c>
-      <c r="G29" s="3">
-        <f t="shared" si="0"/>
-        <v>158</v>
-      </c>
-      <c r="H29" s="3">
-        <f t="shared" si="1"/>
-        <v>31.6</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="15.6">
-      <c r="A30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4">
-        <v>1088</v>
-      </c>
-      <c r="C30" s="2">
-        <v>2499</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="F30" s="3">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G30" s="3">
-        <f t="shared" si="0"/>
-        <v>2.9999999999999991</v>
-      </c>
-      <c r="H30" s="3">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999993</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="15.6">
-      <c r="A31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="4">
-        <v>1030</v>
-      </c>
-      <c r="C31" s="2">
-        <v>4421</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" s="3">
-        <v>45</v>
-      </c>
-      <c r="F31" s="3">
-        <v>87</v>
-      </c>
-      <c r="G31" s="3">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="H31" s="3">
-        <f t="shared" si="1"/>
-        <v>8.4</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="15.6">
-      <c r="A32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="4">
-        <v>1031</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1109</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="U32" s="5"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
     </row>
     <row r="33" spans="1:11" ht="15.6">
       <c r="A33" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="4">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="C33" s="2">
-        <v>2877</v>
+        <v>2242</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E33" s="3">
-        <v>11.4</v>
+        <v>60</v>
       </c>
       <c r="F33" s="3">
-        <v>16.3</v>
+        <v>124</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <f>F33-E33</f>
+        <v>64</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F33&gt;50, G33*0.2, G33*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.6">
       <c r="A34" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B34" s="4">
-        <v>1033</v>
+        <v>1102</v>
       </c>
       <c r="C34" s="2">
-        <v>9822</v>
+        <v>2242</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E34" s="3">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="F34" s="3">
-        <v>98.4</v>
+        <v>124</v>
       </c>
       <c r="G34" s="3">
-        <f t="shared" ref="G34:G65" si="2">F34-E34</f>
-        <v>40.100000000000009</v>
+        <f>F34-E34</f>
+        <v>64</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" ref="H34:H65" si="3">IF(F34&gt;50, G34*0.2, G34*0.1)</f>
-        <v>8.0200000000000014</v>
+        <f>IF(F34&gt;50, G34*0.2, G34*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>2</v>
@@ -7013,35 +7505,35 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.6">
       <c r="A35" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B35" s="4">
-        <v>1034</v>
+        <v>1114</v>
       </c>
       <c r="C35" s="2">
-        <v>2877</v>
+        <v>2242</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E35" s="3">
-        <v>11.4</v>
+        <v>60</v>
       </c>
       <c r="F35" s="3">
-        <v>16.3</v>
+        <v>124</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" si="2"/>
-        <v>4.9000000000000004</v>
+        <f>F35-E35</f>
+        <v>64</v>
       </c>
       <c r="H35" s="3">
-        <f t="shared" si="3"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F35&gt;50, G35*0.2, G35*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>2</v>
@@ -7050,35 +7542,35 @@
         <v>1</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15.6">
       <c r="A36" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B36" s="4">
-        <v>1029</v>
+        <v>1142</v>
       </c>
       <c r="C36" s="2">
-        <v>2499</v>
+        <v>2242</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E36" s="3">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="F36" s="3">
-        <v>9.1999999999999993</v>
+        <v>124</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F36-E36</f>
+        <v>64</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F36&gt;50, G36*0.2, G36*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>2</v>
@@ -7087,35 +7579,35 @@
         <v>1</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.6">
       <c r="A37" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B37" s="4">
-        <v>1036</v>
+        <v>1151</v>
       </c>
       <c r="C37" s="2">
-        <v>2499</v>
+        <v>2242</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E37" s="3">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="F37" s="3">
-        <v>9.1999999999999993</v>
+        <v>124</v>
       </c>
       <c r="G37" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F37-E37</f>
+        <v>64</v>
       </c>
       <c r="H37" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F37&gt;50, G37*0.2, G37*0.1)</f>
+        <v>12.8</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>2</v>
@@ -7124,220 +7616,220 @@
         <v>1</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15.6">
       <c r="A38" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B38" s="4">
-        <v>1037</v>
+        <v>1001</v>
       </c>
       <c r="C38" s="2">
-        <v>6622</v>
+        <v>9822</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E38" s="3">
-        <v>42</v>
+        <v>58.3</v>
       </c>
       <c r="F38" s="3">
-        <v>77</v>
+        <v>98.4</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f>F38-E38</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H38" s="3">
-        <f t="shared" si="3"/>
+        <f>IF(F38&gt;50, G38*0.2, G38*0.1)</f>
+        <v>8.0200000000000014</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="J38" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15.6">
       <c r="A39" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B39" s="4">
-        <v>1038</v>
+        <v>1113</v>
       </c>
       <c r="C39" s="2">
-        <v>2499</v>
+        <v>9822</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E39" s="3">
-        <v>6.2</v>
+        <v>58.3</v>
       </c>
       <c r="F39" s="3">
-        <v>9.1999999999999993</v>
+        <v>98.4</v>
       </c>
       <c r="G39" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F39-E39</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H39" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F39&gt;50, G39*0.2, G39*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15.6">
       <c r="A40" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B40" s="4">
-        <v>1039</v>
+        <v>1133</v>
       </c>
       <c r="C40" s="2">
-        <v>2877</v>
+        <v>9822</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E40" s="3">
-        <v>11.4</v>
+        <v>58.3</v>
       </c>
       <c r="F40" s="3">
-        <v>16.3</v>
+        <v>98.4</v>
       </c>
       <c r="G40" s="3">
-        <f t="shared" si="2"/>
-        <v>4.9000000000000004</v>
+        <f>F40-E40</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H40" s="3">
-        <f t="shared" si="3"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F40&gt;50, G40*0.2, G40*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15.6">
       <c r="A41" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B41" s="4">
-        <v>1040</v>
+        <v>1147</v>
       </c>
       <c r="C41" s="2">
-        <v>1109</v>
+        <v>9822</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E41" s="3">
-        <v>3</v>
+        <v>58.3</v>
       </c>
       <c r="F41" s="3">
-        <v>8</v>
+        <v>98.4</v>
       </c>
       <c r="G41" s="3">
-        <f t="shared" si="2"/>
+        <f>F41-E41</f>
+        <v>40.100000000000009</v>
+      </c>
+      <c r="H41" s="3">
+        <f>IF(F41&gt;50, G41*0.2, G41*0.1)</f>
+        <v>8.0200000000000014</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K41" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H41" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15.6">
       <c r="A42" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B42" s="4">
-        <v>1057</v>
+        <v>1006</v>
       </c>
       <c r="C42" s="2">
-        <v>2499</v>
+        <v>9822</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E42" s="3">
-        <v>6.2</v>
+        <v>58.3</v>
       </c>
       <c r="F42" s="3">
-        <v>9.1999999999999993</v>
+        <v>98.4</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F42-E42</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H42" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F42&gt;50, G42*0.2, G42*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15.6">
       <c r="A43" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B43" s="4">
-        <v>1042</v>
+        <v>1085</v>
       </c>
       <c r="C43" s="2">
-        <v>8722</v>
+        <v>9822</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E43" s="3">
-        <v>344</v>
+        <v>58.3</v>
       </c>
       <c r="F43" s="3">
-        <v>502</v>
+        <v>98.4</v>
       </c>
       <c r="G43" s="3">
-        <f t="shared" si="2"/>
-        <v>158</v>
+        <f>F43-E43</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H43" s="3">
-        <f t="shared" si="3"/>
-        <v>31.6</v>
+        <f>IF(F43&gt;50, G43*0.2, G43*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>10</v>
@@ -7346,35 +7838,35 @@
         <v>9</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15.6">
       <c r="A44" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B44" s="4">
-        <v>1043</v>
+        <v>1108</v>
       </c>
       <c r="C44" s="2">
-        <v>2242</v>
+        <v>9822</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E44" s="3">
-        <v>60</v>
+        <v>58.3</v>
       </c>
       <c r="F44" s="3">
-        <v>124</v>
+        <v>98.4</v>
       </c>
       <c r="G44" s="3">
-        <f t="shared" si="2"/>
-        <v>64</v>
+        <f>F44-E44</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H44" s="3">
-        <f t="shared" si="3"/>
-        <v>12.8</v>
+        <f>IF(F44&gt;50, G44*0.2, G44*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>10</v>
@@ -7383,35 +7875,35 @@
         <v>9</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15.6">
       <c r="A45" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B45" s="4">
-        <v>1044</v>
+        <v>1123</v>
       </c>
       <c r="C45" s="2">
-        <v>2877</v>
+        <v>9822</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E45" s="3">
-        <v>11.4</v>
+        <v>58.3</v>
       </c>
       <c r="F45" s="3">
-        <v>16.3</v>
+        <v>98.4</v>
       </c>
       <c r="G45" s="3">
-        <f t="shared" si="2"/>
-        <v>4.9000000000000004</v>
+        <f>F45-E45</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H45" s="3">
-        <f t="shared" si="3"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F45&gt;50, G45*0.2, G45*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>10</v>
@@ -7420,41 +7912,41 @@
         <v>9</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.6">
       <c r="A46" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B46" s="4">
-        <v>1045</v>
+        <v>1134</v>
       </c>
       <c r="C46" s="2">
-        <v>8722</v>
+        <v>9822</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E46" s="3">
-        <v>344</v>
+        <v>58.3</v>
       </c>
       <c r="F46" s="3">
-        <v>502</v>
+        <v>98.4</v>
       </c>
       <c r="G46" s="3">
-        <f t="shared" si="2"/>
-        <v>158</v>
+        <f>F46-E46</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H46" s="3">
-        <f t="shared" si="3"/>
-        <v>31.6</v>
+        <f>IF(F46&gt;50, G46*0.2, G46*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>16</v>
@@ -7462,73 +7954,73 @@
     </row>
     <row r="47" spans="1:11" ht="15.6">
       <c r="A47" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B47" s="4">
-        <v>1046</v>
+        <v>1164</v>
       </c>
       <c r="C47" s="2">
-        <v>6119</v>
+        <v>9822</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E47" s="3">
+        <v>58.3</v>
+      </c>
+      <c r="F47" s="3">
+        <v>98.4</v>
+      </c>
+      <c r="G47" s="3">
+        <f>F47-E47</f>
+        <v>40.100000000000009</v>
+      </c>
+      <c r="H47" s="3">
+        <f>IF(F47&gt;50, G47*0.2, G47*0.1)</f>
+        <v>8.0200000000000014</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F47" s="3">
-        <v>14</v>
-      </c>
-      <c r="G47" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H47" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="K47" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15.6">
       <c r="A48" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B48" s="4">
-        <v>1047</v>
+        <v>1165</v>
       </c>
       <c r="C48" s="2">
-        <v>6622</v>
+        <v>9822</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E48" s="3">
-        <v>42</v>
+        <v>58.3</v>
       </c>
       <c r="F48" s="3">
-        <v>77</v>
+        <v>98.4</v>
       </c>
       <c r="G48" s="3">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f>F48-E48</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f>IF(F48&gt;50, G48*0.2, G48*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>16</v>
@@ -7536,73 +8028,73 @@
     </row>
     <row r="49" spans="1:11" ht="15.6">
       <c r="A49" s="5" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B49" s="4">
-        <v>1048</v>
+        <v>1168</v>
       </c>
       <c r="C49" s="2">
-        <v>8722</v>
+        <v>9822</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E49" s="3">
-        <v>344</v>
+        <v>58.3</v>
       </c>
       <c r="F49" s="3">
-        <v>502</v>
+        <v>98.4</v>
       </c>
       <c r="G49" s="3">
-        <f t="shared" si="2"/>
-        <v>158</v>
+        <f>F49-E49</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H49" s="3">
-        <f t="shared" si="3"/>
-        <v>31.6</v>
+        <f>IF(F49&gt;50, G49*0.2, G49*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15.6">
       <c r="A50" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B50" s="4">
-        <v>1105</v>
+        <v>1077</v>
       </c>
       <c r="C50" s="2">
-        <v>2499</v>
+        <v>9822</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E50" s="3">
-        <v>6.2</v>
+        <v>58.3</v>
       </c>
       <c r="F50" s="3">
-        <v>9.1999999999999993</v>
+        <v>98.4</v>
       </c>
       <c r="G50" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F50-E50</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H50" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F50&gt;50, G50*0.2, G50*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>16</v>
@@ -7610,147 +8102,147 @@
     </row>
     <row r="51" spans="1:11" ht="15.6">
       <c r="A51" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B51" s="4">
-        <v>1050</v>
+        <v>1129</v>
       </c>
       <c r="C51" s="2">
-        <v>2877</v>
+        <v>9822</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3">
-        <v>11.4</v>
+        <v>58.3</v>
       </c>
       <c r="F51" s="3">
-        <v>16.3</v>
+        <v>98.4</v>
       </c>
       <c r="G51" s="3">
-        <f t="shared" si="2"/>
-        <v>4.9000000000000004</v>
+        <f>F51-E51</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H51" s="3">
-        <f t="shared" si="3"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F51&gt;50, G51*0.2, G51*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.6">
       <c r="A52" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B52" s="4">
-        <v>1051</v>
+        <v>1143</v>
       </c>
       <c r="C52" s="2">
-        <v>6119</v>
+        <v>9822</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E52" s="3">
-        <v>9</v>
+        <v>58.3</v>
       </c>
       <c r="F52" s="3">
-        <v>14</v>
+        <v>98.4</v>
       </c>
       <c r="G52" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F52-E52</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H52" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F52&gt;50, G52*0.2, G52*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15.6">
       <c r="A53" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B53" s="4">
-        <v>1052</v>
+        <v>1160</v>
       </c>
       <c r="C53" s="2">
-        <v>6622</v>
+        <v>9822</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E53" s="3">
-        <v>42</v>
+        <v>58.3</v>
       </c>
       <c r="F53" s="3">
-        <v>77</v>
+        <v>98.4</v>
       </c>
       <c r="G53" s="3">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f>F53-E53</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H53" s="3">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f>IF(F53&gt;50, G53*0.2, G53*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15.6">
       <c r="A54" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B54" s="4">
-        <v>1053</v>
+        <v>1033</v>
       </c>
       <c r="C54" s="2">
-        <v>2242</v>
+        <v>9822</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E54" s="3">
-        <v>60</v>
+        <v>58.3</v>
       </c>
       <c r="F54" s="3">
-        <v>124</v>
+        <v>98.4</v>
       </c>
       <c r="G54" s="3">
-        <f t="shared" si="2"/>
-        <v>64</v>
+        <f>F54-E54</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H54" s="3">
-        <f t="shared" si="3"/>
-        <v>12.8</v>
+        <f>IF(F54&gt;50, G54*0.2, G54*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>5</v>
@@ -7758,67 +8250,67 @@
     </row>
     <row r="55" spans="1:11" ht="15.6">
       <c r="A55" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B55" s="4">
-        <v>1054</v>
+        <v>1106</v>
       </c>
       <c r="C55" s="2">
-        <v>4421</v>
+        <v>9822</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E55" s="3">
-        <v>45</v>
+        <v>58.3</v>
       </c>
       <c r="F55" s="3">
-        <v>87</v>
+        <v>98.4</v>
       </c>
       <c r="G55" s="3">
-        <f t="shared" si="2"/>
-        <v>42</v>
+        <f>F55-E55</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H55" s="3">
-        <f t="shared" si="3"/>
-        <v>8.4</v>
+        <f>IF(F55&gt;50, G55*0.2, G55*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15.6">
       <c r="A56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B56" s="4">
-        <v>1055</v>
+        <v>1118</v>
       </c>
       <c r="C56" s="2">
-        <v>6119</v>
+        <v>9822</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E56" s="3">
-        <v>9</v>
+        <v>58.3</v>
       </c>
       <c r="F56" s="3">
-        <v>14</v>
+        <v>98.4</v>
       </c>
       <c r="G56" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F56-E56</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H56" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F56&gt;50, G56*0.2, G56*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>2</v>
@@ -7827,41 +8319,41 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15.6">
       <c r="A57" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B57" s="4">
-        <v>1056</v>
+        <v>1137</v>
       </c>
       <c r="C57" s="2">
-        <v>1109</v>
+        <v>9822</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>58.3</v>
       </c>
       <c r="F57" s="3">
-        <v>8</v>
+        <v>98.4</v>
       </c>
       <c r="G57" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F57-E57</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H57" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F57&gt;50, G57*0.2, G57*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>5</v>
@@ -7869,141 +8361,141 @@
     </row>
     <row r="58" spans="1:11" ht="15.6">
       <c r="A58" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B58" s="4">
-        <v>1035</v>
+        <v>1154</v>
       </c>
       <c r="C58" s="2">
-        <v>2499</v>
+        <v>9822</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E58" s="3">
-        <v>6.2</v>
+        <v>58.3</v>
       </c>
       <c r="F58" s="3">
-        <v>9.1999999999999993</v>
+        <v>98.4</v>
       </c>
       <c r="G58" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F58-E58</f>
+        <v>40.100000000000009</v>
       </c>
       <c r="H58" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F58&gt;50, G58*0.2, G58*0.1)</f>
+        <v>8.0200000000000014</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15.6">
       <c r="A59" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B59" s="4">
-        <v>1058</v>
+        <v>1152</v>
       </c>
       <c r="C59" s="2">
-        <v>6119</v>
+        <v>4421</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F59" s="3">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="G59" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F59-E59</f>
+        <v>42</v>
       </c>
       <c r="H59" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F59&gt;50, G59*0.2, G59*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="15.6">
       <c r="A60" s="5" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B60" s="4">
-        <v>1059</v>
+        <v>1170</v>
       </c>
       <c r="C60" s="2">
-        <v>2242</v>
+        <v>4421</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E60" s="3">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F60" s="3">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="G60" s="3">
-        <f t="shared" si="2"/>
-        <v>64</v>
+        <f>F60-E60</f>
+        <v>42</v>
       </c>
       <c r="H60" s="3">
-        <f t="shared" si="3"/>
-        <v>12.8</v>
+        <f>IF(F60&gt;50, G60*0.2, G60*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="15.6">
       <c r="A61" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B61" s="4">
-        <v>1060</v>
+        <v>1012</v>
       </c>
       <c r="C61" s="2">
-        <v>6119</v>
+        <v>4421</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E61" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F61" s="3">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="G61" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F61-E61</f>
+        <v>42</v>
       </c>
       <c r="H61" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F61&gt;50, G61*0.2, G61*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>10</v>
@@ -8012,35 +8504,35 @@
         <v>9</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15.6">
       <c r="A62" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B62" s="4">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="C62" s="2">
-        <v>1109</v>
+        <v>4421</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E62" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F62" s="3">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G62" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F62-E62</f>
+        <v>42</v>
       </c>
       <c r="H62" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F62&gt;50, G62*0.2, G62*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>10</v>
@@ -8054,67 +8546,67 @@
     </row>
     <row r="63" spans="1:11" ht="15.6">
       <c r="A63" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B63" s="4">
-        <v>1064</v>
+        <v>1080</v>
       </c>
       <c r="C63" s="2">
-        <v>2499</v>
+        <v>4421</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E63" s="3">
-        <v>6.2</v>
+        <v>45</v>
       </c>
       <c r="F63" s="3">
-        <v>9.1999999999999993</v>
+        <v>87</v>
       </c>
       <c r="G63" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F63-E63</f>
+        <v>42</v>
       </c>
       <c r="H63" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F63&gt;50, G63*0.2, G63*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15.6">
       <c r="A64" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B64" s="4">
-        <v>1063</v>
+        <v>1121</v>
       </c>
       <c r="C64" s="2">
-        <v>1109</v>
+        <v>4421</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F64" s="3">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G64" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>F64-E64</f>
+        <v>42</v>
       </c>
       <c r="H64" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>IF(F64&gt;50, G64*0.2, G64*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>10</v>
@@ -8123,41 +8615,41 @@
         <v>9</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15.6">
       <c r="A65" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B65" s="4">
-        <v>1070</v>
+        <v>1124</v>
       </c>
       <c r="C65" s="2">
-        <v>2499</v>
+        <v>4421</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E65" s="3">
-        <v>6.2</v>
+        <v>45</v>
       </c>
       <c r="F65" s="3">
-        <v>9.1999999999999993</v>
+        <v>87</v>
       </c>
       <c r="G65" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9999999999999991</v>
+        <f>F65-E65</f>
+        <v>42</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" si="3"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F65&gt;50, G65*0.2, G65*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>16</v>
@@ -8165,67 +8657,67 @@
     </row>
     <row r="66" spans="1:11" ht="15.6">
       <c r="A66" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B66" s="4">
-        <v>1095</v>
+        <v>1139</v>
       </c>
       <c r="C66" s="2">
-        <v>2499</v>
+        <v>4421</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E66" s="3">
-        <v>6.2</v>
+        <v>45</v>
       </c>
       <c r="F66" s="3">
-        <v>9.1999999999999993</v>
+        <v>87</v>
       </c>
       <c r="G66" s="3">
-        <f t="shared" ref="G66:G97" si="4">F66-E66</f>
-        <v>2.9999999999999991</v>
+        <f>F66-E66</f>
+        <v>42</v>
       </c>
       <c r="H66" s="3">
-        <f t="shared" ref="H66:H97" si="5">IF(F66&gt;50, G66*0.2, G66*0.1)</f>
-        <v>0.29999999999999993</v>
+        <f>IF(F66&gt;50, G66*0.2, G66*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15.6">
       <c r="A67" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B67" s="4">
-        <v>1066</v>
+        <v>1155</v>
       </c>
       <c r="C67" s="2">
-        <v>2877</v>
+        <v>4421</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E67" s="3">
-        <v>11.4</v>
+        <v>45</v>
       </c>
       <c r="F67" s="3">
-        <v>16.3</v>
+        <v>87</v>
       </c>
       <c r="G67" s="3">
-        <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <f>F67-E67</f>
+        <v>42</v>
       </c>
       <c r="H67" s="3">
-        <f t="shared" si="5"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F67&gt;50, G67*0.2, G67*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>10</v>
@@ -8234,226 +8726,226 @@
         <v>9</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="15.6">
       <c r="A68" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B68" s="4">
-        <v>1067</v>
+        <v>1130</v>
       </c>
       <c r="C68" s="2">
-        <v>2877</v>
+        <v>4421</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E68" s="3">
-        <v>11.4</v>
+        <v>45</v>
       </c>
       <c r="F68" s="3">
-        <v>16.3</v>
+        <v>87</v>
       </c>
       <c r="G68" s="3">
-        <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <f>F68-E68</f>
+        <v>42</v>
       </c>
       <c r="H68" s="3">
-        <f t="shared" si="5"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F68&gt;50, G68*0.2, G68*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="15.6">
       <c r="A69" s="5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B69" s="4">
-        <v>1068</v>
+        <v>1145</v>
       </c>
       <c r="C69" s="2">
-        <v>6119</v>
+        <v>4421</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E69" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F69" s="3">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="G69" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F69-E69</f>
+        <v>42</v>
       </c>
       <c r="H69" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F69&gt;50, G69*0.2, G69*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="15.6">
       <c r="A70" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B70" s="4">
-        <v>1069</v>
+        <v>1030</v>
       </c>
       <c r="C70" s="2">
-        <v>1109</v>
+        <v>4421</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F70" s="3">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G70" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F70-E70</f>
+        <v>42</v>
       </c>
       <c r="H70" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F70&gt;50, G70*0.2, G70*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="15.6">
       <c r="A71" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B71" s="4">
-        <v>1003</v>
+        <v>1140</v>
       </c>
       <c r="C71" s="2">
-        <v>2499</v>
+        <v>4421</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E71" s="3">
-        <v>6.2</v>
+        <v>45</v>
       </c>
       <c r="F71" s="3">
-        <v>9.1999999999999993</v>
+        <v>87</v>
       </c>
       <c r="G71" s="3">
-        <f t="shared" si="4"/>
-        <v>2.9999999999999991</v>
+        <f>F71-E71</f>
+        <v>42</v>
       </c>
       <c r="H71" s="3">
-        <f t="shared" si="5"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F71&gt;50, G71*0.2, G71*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="15.6">
       <c r="A72" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B72" s="4">
-        <v>1071</v>
+        <v>1161</v>
       </c>
       <c r="C72" s="2">
-        <v>1109</v>
+        <v>4421</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E72" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F72" s="3">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G72" s="3">
-        <f t="shared" si="4"/>
+        <f>F72-E72</f>
+        <v>42</v>
+      </c>
+      <c r="H72" s="3">
+        <f>IF(F72&gt;50, G72*0.2, G72*0.1)</f>
+        <v>8.4</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H72" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="15.6">
       <c r="A73" s="5" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B73" s="4">
-        <v>1072</v>
+        <v>1171</v>
       </c>
       <c r="C73" s="2">
-        <v>1109</v>
+        <v>4421</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E73" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F73" s="3">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G73" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F73-E73</f>
+        <v>42</v>
       </c>
       <c r="H73" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F73&gt;50, G73*0.2, G73*0.1)</f>
+        <v>8.4</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>0</v>
@@ -8461,10 +8953,10 @@
     </row>
     <row r="74" spans="1:11" ht="15.6">
       <c r="A74" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B74" s="4">
-        <v>1073</v>
+        <v>1052</v>
       </c>
       <c r="C74" s="2">
         <v>6622</v>
@@ -8479,11 +8971,11 @@
         <v>77</v>
       </c>
       <c r="G74" s="3">
-        <f t="shared" si="4"/>
+        <f>F74-E74</f>
         <v>35</v>
       </c>
       <c r="H74" s="3">
-        <f t="shared" si="5"/>
+        <f>IF(F74&gt;50, G74*0.2, G74*0.1)</f>
         <v>7</v>
       </c>
       <c r="I74" s="2" t="s">
@@ -8493,7 +8985,7 @@
         <v>9</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="15.6">
@@ -8501,27 +8993,27 @@
         <v>30</v>
       </c>
       <c r="B75" s="4">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C75" s="2">
-        <v>2877</v>
+        <v>6622</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E75" s="3">
-        <v>11.4</v>
+        <v>42</v>
       </c>
       <c r="F75" s="3">
-        <v>16.3</v>
+        <v>77</v>
       </c>
       <c r="G75" s="3">
-        <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <f>F75-E75</f>
+        <v>35</v>
       </c>
       <c r="H75" s="3">
-        <f t="shared" si="5"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F75&gt;50, G75*0.2, G75*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>10</v>
@@ -8530,294 +9022,294 @@
         <v>9</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="15.6">
       <c r="A76" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B76" s="4">
-        <v>1075</v>
+        <v>1112</v>
       </c>
       <c r="C76" s="2">
-        <v>1109</v>
+        <v>6622</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E76" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="G76" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F76-E76</f>
+        <v>35</v>
       </c>
       <c r="H76" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F76&gt;50, G76*0.2, G76*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="15.6">
       <c r="A77" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B77" s="4">
-        <v>1076</v>
+        <v>1116</v>
       </c>
       <c r="C77" s="2">
-        <v>1109</v>
+        <v>6622</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E77" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F77" s="3">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="G77" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F77-E77</f>
+        <v>35</v>
       </c>
       <c r="H77" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F77&gt;50, G77*0.2, G77*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15.6">
       <c r="A78" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B78" s="4">
-        <v>1077</v>
+        <v>1159</v>
       </c>
       <c r="C78" s="2">
-        <v>9822</v>
+        <v>6622</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E78" s="3">
-        <v>58.3</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3">
-        <v>98.4</v>
+        <v>77</v>
       </c>
       <c r="G78" s="3">
-        <f t="shared" si="4"/>
-        <v>40.100000000000009</v>
+        <f>F78-E78</f>
+        <v>35</v>
       </c>
       <c r="H78" s="3">
-        <f t="shared" si="5"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F78&gt;50, G78*0.2, G78*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="15.6">
       <c r="A79" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B79" s="4">
-        <v>1078</v>
+        <v>1047</v>
       </c>
       <c r="C79" s="2">
-        <v>2877</v>
+        <v>6622</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E79" s="3">
-        <v>11.4</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3">
-        <v>16.3</v>
+        <v>77</v>
       </c>
       <c r="G79" s="3">
-        <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <f>F79-E79</f>
+        <v>35</v>
       </c>
       <c r="H79" s="3">
-        <f t="shared" si="5"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F79&gt;50, G79*0.2, G79*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="15.6">
       <c r="A80" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B80" s="4">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="C80" s="2">
-        <v>2877</v>
+        <v>6622</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E80" s="3">
-        <v>11.4</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3">
-        <v>16.3</v>
+        <v>77</v>
       </c>
       <c r="G80" s="3">
-        <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <f>F80-E80</f>
+        <v>35</v>
       </c>
       <c r="H80" s="3">
-        <f t="shared" si="5"/>
-        <v>0.49000000000000005</v>
+        <f>IF(F80&gt;50, G80*0.2, G80*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="15.6">
       <c r="A81" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B81" s="4">
-        <v>1080</v>
+        <v>1037</v>
       </c>
       <c r="C81" s="2">
-        <v>4421</v>
+        <v>6622</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E81" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F81" s="3">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G81" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
+        <f>F81-E81</f>
+        <v>35</v>
       </c>
       <c r="H81" s="3">
-        <f t="shared" si="5"/>
-        <v>8.4</v>
+        <f>IF(F81&gt;50, G81*0.2, G81*0.1)</f>
+        <v>7</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="15.6">
       <c r="A82" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B82" s="4">
-        <v>1081</v>
+        <v>1128</v>
       </c>
       <c r="C82" s="2">
-        <v>6119</v>
+        <v>6622</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E82" s="3">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="F82" s="3">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="G82" s="3">
-        <f t="shared" si="4"/>
+        <f>F82-E82</f>
+        <v>35</v>
+      </c>
+      <c r="H82" s="3">
+        <f>IF(F82&gt;50, G82*0.2, G82*0.1)</f>
+        <v>7</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K82" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H82" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="15.6">
       <c r="A83" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B83" s="4">
-        <v>1082</v>
+        <v>1032</v>
       </c>
       <c r="C83" s="2">
-        <v>1109</v>
+        <v>2877</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E83" s="3">
-        <v>3</v>
+        <v>11.4</v>
       </c>
       <c r="F83" s="3">
-        <v>8</v>
+        <v>16.3</v>
       </c>
       <c r="G83" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F83-E83</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H83" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F83&gt;50, G83*0.2, G83*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>7</v>
@@ -8826,35 +9318,35 @@
         <v>6</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="15.6">
       <c r="A84" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B84" s="4">
-        <v>1083</v>
+        <v>1050</v>
       </c>
       <c r="C84" s="2">
-        <v>1109</v>
+        <v>2877</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E84" s="3">
-        <v>3</v>
+        <v>11.4</v>
       </c>
       <c r="F84" s="3">
-        <v>8</v>
+        <v>16.3</v>
       </c>
       <c r="G84" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F84-E84</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H84" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F84&gt;50, G84*0.2, G84*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>7</v>
@@ -8863,7 +9355,7 @@
         <v>6</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="15.6">
@@ -8871,27 +9363,27 @@
         <v>29</v>
       </c>
       <c r="B85" s="4">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="C85" s="2">
-        <v>6119</v>
+        <v>2877</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E85" s="3">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="F85" s="3">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="G85" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F85-E85</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H85" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F85&gt;50, G85*0.2, G85*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>7</v>
@@ -8900,35 +9392,35 @@
         <v>6</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="15.6">
       <c r="A86" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B86" s="4">
-        <v>1085</v>
+        <v>1008</v>
       </c>
       <c r="C86" s="2">
-        <v>9822</v>
+        <v>2877</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E86" s="3">
-        <v>58.3</v>
+        <v>11.4</v>
       </c>
       <c r="F86" s="3">
-        <v>98.4</v>
+        <v>16.3</v>
       </c>
       <c r="G86" s="3">
-        <f t="shared" si="4"/>
-        <v>40.100000000000009</v>
+        <f>F86-E86</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H86" s="3">
-        <f t="shared" si="5"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F86&gt;50, G86*0.2, G86*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>10</v>
@@ -8937,72 +9429,72 @@
         <v>9</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="15.6">
       <c r="A87" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B87" s="4">
-        <v>1086</v>
+        <v>1022</v>
       </c>
       <c r="C87" s="2">
-        <v>1109</v>
+        <v>2877</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E87" s="3">
-        <v>3</v>
+        <v>11.4</v>
       </c>
       <c r="F87" s="3">
+        <v>16.3</v>
+      </c>
+      <c r="G87" s="3">
+        <f>F87-E87</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H87" s="3">
+        <f>IF(F87&gt;50, G87*0.2, G87*0.1)</f>
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K87" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="G87" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H87" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="15.6">
       <c r="A88" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B88" s="4">
-        <v>1016</v>
+        <v>1044</v>
       </c>
       <c r="C88" s="2">
-        <v>2499</v>
+        <v>2877</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E88" s="3">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="F88" s="3">
-        <v>9.1999999999999993</v>
+        <v>16.3</v>
       </c>
       <c r="G88" s="3">
-        <f t="shared" si="4"/>
-        <v>2.9999999999999991</v>
+        <f>F88-E88</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H88" s="3">
-        <f t="shared" si="5"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F88&gt;50, G88*0.2, G88*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>10</v>
@@ -9016,30 +9508,30 @@
     </row>
     <row r="89" spans="1:11" ht="15.6">
       <c r="A89" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B89" s="4">
-        <v>1019</v>
+        <v>1066</v>
       </c>
       <c r="C89" s="2">
-        <v>2499</v>
+        <v>2877</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E89" s="3">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="F89" s="3">
-        <v>9.1999999999999993</v>
+        <v>16.3</v>
       </c>
       <c r="G89" s="3">
-        <f t="shared" si="4"/>
-        <v>2.9999999999999991</v>
+        <f>F89-E89</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H89" s="3">
-        <f t="shared" si="5"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F89&gt;50, G89*0.2, G89*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>10</v>
@@ -9048,35 +9540,35 @@
         <v>9</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="15.6">
       <c r="A90" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B90" s="4">
-        <v>1089</v>
+        <v>1067</v>
       </c>
       <c r="C90" s="2">
-        <v>6119</v>
+        <v>2877</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E90" s="3">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="F90" s="3">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="G90" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F90-E90</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H90" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F90&gt;50, G90*0.2, G90*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>10</v>
@@ -9085,15 +9577,15 @@
         <v>9</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="15.6">
       <c r="A91" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B91" s="4">
-        <v>1090</v>
+        <v>1074</v>
       </c>
       <c r="C91" s="2">
         <v>2877</v>
@@ -9108,21 +9600,21 @@
         <v>16.3</v>
       </c>
       <c r="G91" s="3">
-        <f t="shared" si="4"/>
+        <f>F91-E91</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H91" s="3">
-        <f t="shared" si="5"/>
+        <f>IF(F91&gt;50, G91*0.2, G91*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="15.6">
@@ -9130,7 +9622,7 @@
         <v>29</v>
       </c>
       <c r="B92" s="4">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C92" s="2">
         <v>2877</v>
@@ -9145,29 +9637,29 @@
         <v>16.3</v>
       </c>
       <c r="G92" s="3">
-        <f t="shared" si="4"/>
+        <f>F92-E92</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H92" s="3">
-        <f t="shared" si="5"/>
+        <f>IF(F92&gt;50, G92*0.2, G92*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="15.6">
       <c r="A93" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B93" s="4">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C93" s="2">
         <v>2877</v>
@@ -9182,11 +9674,11 @@
         <v>16.3</v>
       </c>
       <c r="G93" s="3">
-        <f t="shared" si="4"/>
+        <f>F93-E93</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H93" s="3">
-        <f t="shared" si="5"/>
+        <f>IF(F93&gt;50, G93*0.2, G93*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I93" s="2" t="s">
@@ -9201,76 +9693,76 @@
     </row>
     <row r="94" spans="1:11" ht="15.6">
       <c r="A94" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B94" s="4">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="C94" s="2">
-        <v>6119</v>
+        <v>2877</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E94" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="F94" s="3">
+        <v>16.3</v>
+      </c>
+      <c r="G94" s="3">
+        <f>F94-E94</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H94" s="3">
+        <f>IF(F94&gt;50, G94*0.2, G94*0.1)</f>
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J94" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F94" s="3">
-        <v>14</v>
-      </c>
-      <c r="G94" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H94" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="K94" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="15.6">
       <c r="A95" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B95" s="4">
-        <v>1094</v>
+        <v>1015</v>
       </c>
       <c r="C95" s="2">
-        <v>6119</v>
+        <v>2877</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E95" s="3">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="F95" s="3">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="G95" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F95-E95</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H95" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F95&gt;50, G95*0.2, G95*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="15.6">
@@ -9278,33 +9770,33 @@
         <v>34</v>
       </c>
       <c r="B96" s="4">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="C96" s="2">
-        <v>2499</v>
+        <v>2877</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E96" s="3">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="F96" s="3">
-        <v>9.1999999999999993</v>
+        <v>16.3</v>
       </c>
       <c r="G96" s="3">
-        <f t="shared" si="4"/>
-        <v>2.9999999999999991</v>
+        <f>F96-E96</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H96" s="3">
-        <f t="shared" si="5"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F96&gt;50, G96*0.2, G96*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>0</v>
@@ -9315,81 +9807,81 @@
         <v>29</v>
       </c>
       <c r="B97" s="4">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="C97" s="2">
-        <v>6119</v>
+        <v>2877</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E97" s="3">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="F97" s="3">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="G97" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f>F97-E97</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H97" s="3">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>IF(F97&gt;50, G97*0.2, G97*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="15.6">
       <c r="A98" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B98" s="4">
-        <v>1097</v>
+        <v>1002</v>
       </c>
       <c r="C98" s="2">
-        <v>9212</v>
+        <v>2877</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E98" s="3">
-        <v>4</v>
+        <v>11.4</v>
       </c>
       <c r="F98" s="3">
-        <v>7</v>
+        <v>16.3</v>
       </c>
       <c r="G98" s="3">
-        <f t="shared" ref="G98:G129" si="6">F98-E98</f>
-        <v>3</v>
+        <f>F98-E98</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H98" s="3">
-        <f t="shared" ref="H98:H129" si="7">IF(F98&gt;50, G98*0.2, G98*0.1)</f>
-        <v>0.30000000000000004</v>
+        <f>IF(F98&gt;50, G98*0.2, G98*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="15.6">
       <c r="A99" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B99" s="4">
-        <v>1098</v>
+        <v>1010</v>
       </c>
       <c r="C99" s="2">
         <v>2877</v>
@@ -9404,11 +9896,11 @@
         <v>16.3</v>
       </c>
       <c r="G99" s="3">
-        <f t="shared" si="6"/>
+        <f>F99-E99</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H99" s="3">
-        <f t="shared" si="7"/>
+        <f>IF(F99&gt;50, G99*0.2, G99*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I99" s="2" t="s">
@@ -9418,15 +9910,15 @@
         <v>1</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="15.6">
       <c r="A100" s="5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B100" s="4">
-        <v>1099</v>
+        <v>1011</v>
       </c>
       <c r="C100" s="2">
         <v>2877</v>
@@ -9441,123 +9933,123 @@
         <v>16.3</v>
       </c>
       <c r="G100" s="3">
-        <f t="shared" si="6"/>
+        <f>F100-E100</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H100" s="3">
-        <f t="shared" si="7"/>
+        <f>IF(F100&gt;50, G100*0.2, G100*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="15.6">
       <c r="A101" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B101" s="4">
-        <v>1100</v>
+        <v>1034</v>
       </c>
       <c r="C101" s="2">
-        <v>6119</v>
+        <v>2877</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E101" s="3">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="F101" s="3">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="G101" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f>F101-E101</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H101" s="3">
-        <f t="shared" si="7"/>
-        <v>0.5</v>
+        <f>IF(F101&gt;50, G101*0.2, G101*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="15.6">
       <c r="A102" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B102" s="4">
-        <v>1065</v>
+        <v>1039</v>
       </c>
       <c r="C102" s="2">
-        <v>2499</v>
+        <v>2877</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E102" s="3">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="F102" s="3">
-        <v>9.1999999999999993</v>
+        <v>16.3</v>
       </c>
       <c r="G102" s="3">
-        <f t="shared" si="6"/>
-        <v>2.9999999999999991</v>
+        <f>F102-E102</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H102" s="3">
-        <f t="shared" si="7"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F102&gt;50, G102*0.2, G102*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="15.6">
       <c r="A103" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B103" s="4">
-        <v>1102</v>
+        <v>1078</v>
       </c>
       <c r="C103" s="2">
-        <v>2242</v>
+        <v>2877</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E103" s="3">
-        <v>60</v>
+        <v>11.4</v>
       </c>
       <c r="F103" s="3">
-        <v>124</v>
+        <v>16.3</v>
       </c>
       <c r="G103" s="3">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f>F103-E103</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H103" s="3">
-        <f t="shared" si="7"/>
-        <v>12.8</v>
+        <f>IF(F103&gt;50, G103*0.2, G103*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>2</v>
@@ -9571,10 +10063,10 @@
     </row>
     <row r="104" spans="1:11" ht="15.6">
       <c r="A104" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B104" s="4">
-        <v>1103</v>
+        <v>1079</v>
       </c>
       <c r="C104" s="2">
         <v>2877</v>
@@ -9589,11 +10081,11 @@
         <v>16.3</v>
       </c>
       <c r="G104" s="3">
-        <f t="shared" si="6"/>
+        <f>F104-E104</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H104" s="3">
-        <f t="shared" si="7"/>
+        <f>IF(F104&gt;50, G104*0.2, G104*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I104" s="2" t="s">
@@ -9603,15 +10095,15 @@
         <v>1</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="15.6">
       <c r="A105" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B105" s="4">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="C105" s="2">
         <v>2877</v>
@@ -9626,21 +10118,21 @@
         <v>16.3</v>
       </c>
       <c r="G105" s="3">
-        <f t="shared" si="6"/>
+        <f>F105-E105</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H105" s="3">
-        <f t="shared" si="7"/>
+        <f>IF(F105&gt;50, G105*0.2, G105*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="15.6">
@@ -9648,110 +10140,110 @@
         <v>24</v>
       </c>
       <c r="B106" s="4">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C106" s="2">
-        <v>2499</v>
+        <v>2877</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E106" s="3">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="F106" s="3">
-        <v>9.1999999999999993</v>
+        <v>16.3</v>
       </c>
       <c r="G106" s="3">
-        <f t="shared" si="6"/>
-        <v>2.9999999999999991</v>
+        <f>F106-E106</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H106" s="3">
-        <f t="shared" si="7"/>
-        <v>0.29999999999999993</v>
+        <f>IF(F106&gt;50, G106*0.2, G106*0.1)</f>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="15.6">
       <c r="A107" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B107" s="4">
-        <v>1106</v>
+        <v>1027</v>
       </c>
       <c r="C107" s="2">
-        <v>9822</v>
+        <v>6119</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E107" s="3">
-        <v>58.3</v>
+        <v>9</v>
       </c>
       <c r="F107" s="3">
-        <v>98.4</v>
+        <v>14</v>
       </c>
       <c r="G107" s="3">
-        <f t="shared" si="6"/>
-        <v>40.100000000000009</v>
+        <f>F107-E107</f>
+        <v>5</v>
       </c>
       <c r="H107" s="3">
-        <f t="shared" si="7"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F107&gt;50, G107*0.2, G107*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="15.6">
       <c r="A108" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B108" s="4">
-        <v>1107</v>
+        <v>1084</v>
       </c>
       <c r="C108" s="2">
-        <v>1109</v>
+        <v>6119</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E108" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F108" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G108" s="3">
-        <f t="shared" si="6"/>
+        <f>F108-E108</f>
         <v>5</v>
       </c>
       <c r="H108" s="3">
-        <f t="shared" si="7"/>
+        <f>IF(F108&gt;50, G108*0.2, G108*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="15.6">
@@ -9759,107 +10251,107 @@
         <v>24</v>
       </c>
       <c r="B109" s="4">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="C109" s="2">
-        <v>9822</v>
+        <v>6119</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E109" s="3">
-        <v>58.3</v>
+        <v>9</v>
       </c>
       <c r="F109" s="3">
-        <v>98.4</v>
+        <v>14</v>
       </c>
       <c r="G109" s="3">
-        <f t="shared" si="6"/>
-        <v>40.100000000000009</v>
+        <f>F109-E109</f>
+        <v>5</v>
       </c>
       <c r="H109" s="3">
-        <f t="shared" si="7"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F109&gt;50, G109*0.2, G109*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="15.6">
       <c r="A110" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B110" s="4">
-        <v>1109</v>
+        <v>1051</v>
       </c>
       <c r="C110" s="2">
-        <v>8722</v>
+        <v>6119</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E110" s="3">
-        <v>344</v>
+        <v>9</v>
       </c>
       <c r="F110" s="3">
-        <v>502</v>
+        <v>14</v>
       </c>
       <c r="G110" s="3">
-        <f t="shared" si="6"/>
-        <v>158</v>
+        <f>F110-E110</f>
+        <v>5</v>
       </c>
       <c r="H110" s="3">
-        <f t="shared" si="7"/>
-        <v>31.6</v>
+        <f>IF(F110&gt;50, G110*0.2, G110*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="15.6">
       <c r="A111" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B111" s="4">
-        <v>1110</v>
+        <v>1060</v>
       </c>
       <c r="C111" s="2">
-        <v>8722</v>
+        <v>6119</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E111" s="3">
-        <v>344</v>
+        <v>9</v>
       </c>
       <c r="F111" s="3">
-        <v>502</v>
+        <v>14</v>
       </c>
       <c r="G111" s="3">
-        <f t="shared" si="6"/>
-        <v>158</v>
+        <f>F111-E111</f>
+        <v>5</v>
       </c>
       <c r="H111" s="3">
-        <f t="shared" si="7"/>
-        <v>31.6</v>
+        <f>IF(F111&gt;50, G111*0.2, G111*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K111" s="2" t="s">
         <v>0</v>
@@ -9867,67 +10359,67 @@
     </row>
     <row r="112" spans="1:11" ht="15.6">
       <c r="A112" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B112" s="4">
-        <v>1111</v>
+        <v>1081</v>
       </c>
       <c r="C112" s="2">
-        <v>6622</v>
+        <v>6119</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E112" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F112" s="3">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G112" s="3">
-        <f t="shared" si="6"/>
-        <v>35</v>
+        <f>F112-E112</f>
+        <v>5</v>
       </c>
       <c r="H112" s="3">
-        <f t="shared" si="7"/>
-        <v>7</v>
+        <f>IF(F112&gt;50, G112*0.2, G112*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="15.6">
       <c r="A113" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B113" s="4">
-        <v>1112</v>
+        <v>1089</v>
       </c>
       <c r="C113" s="2">
-        <v>6622</v>
+        <v>6119</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E113" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F113" s="3">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G113" s="3">
-        <f t="shared" si="6"/>
-        <v>35</v>
+        <f>F113-E113</f>
+        <v>5</v>
       </c>
       <c r="H113" s="3">
-        <f t="shared" si="7"/>
-        <v>7</v>
+        <f>IF(F113&gt;50, G113*0.2, G113*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>10</v>
@@ -9936,41 +10428,41 @@
         <v>9</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="15.6">
       <c r="A114" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B114" s="4">
-        <v>1113</v>
+        <v>1094</v>
       </c>
       <c r="C114" s="2">
-        <v>9822</v>
+        <v>6119</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E114" s="3">
-        <v>58.3</v>
+        <v>9</v>
       </c>
       <c r="F114" s="3">
-        <v>98.4</v>
+        <v>14</v>
       </c>
       <c r="G114" s="3">
-        <f t="shared" si="6"/>
-        <v>40.100000000000009</v>
+        <f>F114-E114</f>
+        <v>5</v>
       </c>
       <c r="H114" s="3">
-        <f t="shared" si="7"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F114&gt;50, G114*0.2, G114*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>5</v>
@@ -9978,36 +10470,36 @@
     </row>
     <row r="115" spans="1:11" ht="15.6">
       <c r="A115" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B115" s="4">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="C115" s="2">
-        <v>2242</v>
+        <v>6119</v>
       </c>
       <c r="D115" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" s="3">
+        <v>9</v>
+      </c>
+      <c r="F115" s="3">
         <v>14</v>
       </c>
-      <c r="E115" s="3">
-        <v>60</v>
-      </c>
-      <c r="F115" s="3">
-        <v>124</v>
-      </c>
       <c r="G115" s="3">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f>F115-E115</f>
+        <v>5</v>
       </c>
       <c r="H115" s="3">
-        <f t="shared" si="7"/>
-        <v>12.8</v>
+        <f>IF(F115&gt;50, G115*0.2, G115*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>16</v>
@@ -10015,141 +10507,141 @@
     </row>
     <row r="116" spans="1:11" ht="15.6">
       <c r="A116" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B116" s="4">
-        <v>1115</v>
+        <v>1026</v>
       </c>
       <c r="C116" s="2">
-        <v>8722</v>
+        <v>6119</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E116" s="3">
-        <v>344</v>
+        <v>9</v>
       </c>
       <c r="F116" s="3">
-        <v>502</v>
+        <v>14</v>
       </c>
       <c r="G116" s="3">
-        <f t="shared" si="6"/>
-        <v>158</v>
+        <f>F116-E116</f>
+        <v>5</v>
       </c>
       <c r="H116" s="3">
-        <f t="shared" si="7"/>
-        <v>31.6</v>
+        <f>IF(F116&gt;50, G116*0.2, G116*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="15.6">
       <c r="A117" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B117" s="4">
-        <v>1116</v>
+        <v>1058</v>
       </c>
       <c r="C117" s="2">
-        <v>6622</v>
+        <v>6119</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E117" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F117" s="3">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G117" s="3">
-        <f t="shared" si="6"/>
-        <v>35</v>
+        <f>F117-E117</f>
+        <v>5</v>
       </c>
       <c r="H117" s="3">
-        <f t="shared" si="7"/>
-        <v>7</v>
+        <f>IF(F117&gt;50, G117*0.2, G117*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="15.6">
       <c r="A118" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B118" s="4">
-        <v>1117</v>
+        <v>1046</v>
       </c>
       <c r="C118" s="2">
-        <v>8722</v>
+        <v>6119</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E118" s="3">
-        <v>344</v>
+        <v>9</v>
       </c>
       <c r="F118" s="3">
-        <v>502</v>
+        <v>14</v>
       </c>
       <c r="G118" s="3">
-        <f t="shared" si="6"/>
-        <v>158</v>
+        <f>F118-E118</f>
+        <v>5</v>
       </c>
       <c r="H118" s="3">
-        <f t="shared" si="7"/>
-        <v>31.6</v>
+        <f>IF(F118&gt;50, G118*0.2, G118*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="15.6">
       <c r="A119" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B119" s="4">
-        <v>1118</v>
+        <v>1055</v>
       </c>
       <c r="C119" s="2">
-        <v>9822</v>
+        <v>6119</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E119" s="3">
-        <v>58.3</v>
+        <v>9</v>
       </c>
       <c r="F119" s="3">
-        <v>98.4</v>
+        <v>14</v>
       </c>
       <c r="G119" s="3">
-        <f t="shared" si="6"/>
-        <v>40.100000000000009</v>
+        <f>F119-E119</f>
+        <v>5</v>
       </c>
       <c r="H119" s="3">
-        <f t="shared" si="7"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F119&gt;50, G119*0.2, G119*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>2</v>
@@ -10158,294 +10650,294 @@
         <v>1</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.6">
       <c r="A120" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B120" s="4">
-        <v>1119</v>
+        <v>1068</v>
       </c>
       <c r="C120" s="2">
-        <v>2242</v>
+        <v>6119</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E120" s="3">
+        <v>9</v>
+      </c>
+      <c r="F120" s="3">
         <v>14</v>
       </c>
-      <c r="E120" s="3">
-        <v>60</v>
-      </c>
-      <c r="F120" s="3">
-        <v>124</v>
-      </c>
       <c r="G120" s="3">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f>F120-E120</f>
+        <v>5</v>
       </c>
       <c r="H120" s="3">
-        <f t="shared" si="7"/>
-        <v>12.8</v>
+        <f>IF(F120&gt;50, G120*0.2, G120*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="15.6">
       <c r="A121" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B121" s="4">
-        <v>1120</v>
+        <v>1093</v>
       </c>
       <c r="C121" s="2">
-        <v>2242</v>
+        <v>6119</v>
       </c>
       <c r="D121" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E121" s="3">
+        <v>9</v>
+      </c>
+      <c r="F121" s="3">
         <v>14</v>
       </c>
-      <c r="E121" s="3">
-        <v>60</v>
-      </c>
-      <c r="F121" s="3">
-        <v>124</v>
-      </c>
       <c r="G121" s="3">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f>F121-E121</f>
+        <v>5</v>
       </c>
       <c r="H121" s="3">
-        <f t="shared" si="7"/>
-        <v>12.8</v>
+        <f>IF(F121&gt;50, G121*0.2, G121*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="15.6">
       <c r="A122" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B122" s="4">
-        <v>1121</v>
+        <v>1041</v>
       </c>
       <c r="C122" s="2">
-        <v>4421</v>
+        <v>2499</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E122" s="3">
-        <v>45</v>
+        <v>6.2</v>
       </c>
       <c r="F122" s="3">
-        <v>87</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G122" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
+        <f>F122-E122</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H122" s="3">
-        <f t="shared" si="7"/>
-        <v>8.4</v>
+        <f>IF(F122&gt;50, G122*0.2, G122*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="15.6">
       <c r="A123" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B123" s="4">
-        <v>1122</v>
+        <v>1049</v>
       </c>
       <c r="C123" s="2">
-        <v>8722</v>
+        <v>2499</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E123" s="3">
-        <v>344</v>
+        <v>6.2</v>
       </c>
       <c r="F123" s="3">
-        <v>502</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G123" s="3">
-        <f t="shared" si="6"/>
-        <v>158</v>
+        <f>F123-E123</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H123" s="3">
-        <f t="shared" si="7"/>
-        <v>31.6</v>
+        <f>IF(F123&gt;50, G123*0.2, G123*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="15.6">
       <c r="A124" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B124" s="4">
-        <v>1123</v>
+        <v>1062</v>
       </c>
       <c r="C124" s="2">
-        <v>9822</v>
+        <v>2499</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E124" s="3">
-        <v>58.3</v>
+        <v>6.2</v>
       </c>
       <c r="F124" s="3">
-        <v>98.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G124" s="3">
-        <f t="shared" si="6"/>
-        <v>40.100000000000009</v>
+        <f>F124-E124</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H124" s="3">
-        <f t="shared" si="7"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F124&gt;50, G124*0.2, G124*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="15.6">
       <c r="A125" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B125" s="4">
-        <v>1124</v>
+        <v>1087</v>
       </c>
       <c r="C125" s="2">
-        <v>4421</v>
+        <v>2499</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E125" s="3">
-        <v>45</v>
+        <v>6.2</v>
       </c>
       <c r="F125" s="3">
-        <v>87</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G125" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
+        <f>F125-E125</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H125" s="3">
-        <f t="shared" si="7"/>
-        <v>8.4</v>
+        <f>IF(F125&gt;50, G125*0.2, G125*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="15.6">
       <c r="A126" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B126" s="4">
-        <v>1125</v>
+        <v>1088</v>
       </c>
       <c r="C126" s="2">
-        <v>2242</v>
+        <v>2499</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E126" s="3">
-        <v>60</v>
+        <v>6.2</v>
       </c>
       <c r="F126" s="3">
-        <v>124</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G126" s="3">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f>F126-E126</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H126" s="3">
-        <f t="shared" si="7"/>
-        <v>12.8</v>
+        <f>IF(F126&gt;50, G126*0.2, G126*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="15.6">
       <c r="A127" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B127" s="4">
-        <v>1126</v>
+        <v>1003</v>
       </c>
       <c r="C127" s="2">
-        <v>9212</v>
+        <v>2499</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E127" s="3">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="F127" s="3">
-        <v>7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G127" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>F127-E127</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H127" s="3">
-        <f t="shared" si="7"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F127&gt;50, G127*0.2, G127*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>10</v>
@@ -10454,115 +10946,115 @@
         <v>9</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="15.6">
       <c r="A128" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B128" s="4">
-        <v>1127</v>
+        <v>1016</v>
       </c>
       <c r="C128" s="2">
-        <v>8722</v>
+        <v>2499</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E128" s="3">
-        <v>344</v>
+        <v>6.2</v>
       </c>
       <c r="F128" s="3">
-        <v>502</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G128" s="3">
-        <f t="shared" si="6"/>
-        <v>158</v>
+        <f>F128-E128</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H128" s="3">
-        <f t="shared" si="7"/>
-        <v>31.6</v>
+        <f>IF(F128&gt;50, G128*0.2, G128*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="15.6">
       <c r="A129" s="5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B129" s="4">
-        <v>1128</v>
+        <v>1019</v>
       </c>
       <c r="C129" s="2">
-        <v>6622</v>
+        <v>2499</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E129" s="3">
-        <v>42</v>
+        <v>6.2</v>
       </c>
       <c r="F129" s="3">
-        <v>77</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G129" s="3">
-        <f t="shared" si="6"/>
-        <v>35</v>
+        <f>F129-E129</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H129" s="3">
-        <f t="shared" si="7"/>
-        <v>7</v>
+        <f>IF(F129&gt;50, G129*0.2, G129*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="15.6">
       <c r="A130" s="5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B130" s="4">
-        <v>1129</v>
+        <v>1020</v>
       </c>
       <c r="C130" s="2">
-        <v>9822</v>
+        <v>2499</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E130" s="3">
-        <v>58.3</v>
+        <v>6.2</v>
       </c>
       <c r="F130" s="3">
-        <v>98.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G130" s="3">
-        <f t="shared" ref="G130:G161" si="8">F130-E130</f>
-        <v>40.100000000000009</v>
+        <f>F130-E130</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H130" s="3">
-        <f t="shared" ref="H130:H161" si="9">IF(F130&gt;50, G130*0.2, G130*0.1)</f>
-        <v>8.0200000000000014</v>
+        <f>IF(F130&gt;50, G130*0.2, G130*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>0</v>
@@ -10570,104 +11062,104 @@
     </row>
     <row r="131" spans="1:11" ht="15.6">
       <c r="A131" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B131" s="4">
-        <v>1130</v>
+        <v>1065</v>
       </c>
       <c r="C131" s="2">
-        <v>4421</v>
+        <v>2499</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E131" s="3">
-        <v>45</v>
+        <v>6.2</v>
       </c>
       <c r="F131" s="3">
-        <v>87</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G131" s="3">
-        <f t="shared" si="8"/>
-        <v>42</v>
+        <f>F131-E131</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H131" s="3">
-        <f t="shared" si="9"/>
-        <v>8.4</v>
+        <f>IF(F131&gt;50, G131*0.2, G131*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="15.6">
       <c r="A132" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B132" s="4">
-        <v>1131</v>
+        <v>1101</v>
       </c>
       <c r="C132" s="2">
-        <v>9212</v>
+        <v>2499</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E132" s="3">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="F132" s="3">
-        <v>7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G132" s="3">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f>F132-E132</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H132" s="3">
-        <f t="shared" si="9"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F132&gt;50, G132*0.2, G132*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="15.6">
       <c r="A133" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B133" s="4">
-        <v>1132</v>
+        <v>1035</v>
       </c>
       <c r="C133" s="2">
-        <v>9212</v>
+        <v>2499</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E133" s="3">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="F133" s="3">
-        <v>7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G133" s="3">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f>F133-E133</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H133" s="3">
-        <f t="shared" si="9"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F133&gt;50, G133*0.2, G133*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>19</v>
@@ -10681,36 +11173,36 @@
     </row>
     <row r="134" spans="1:11" ht="15.6">
       <c r="A134" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B134" s="4">
-        <v>1133</v>
+        <v>1064</v>
       </c>
       <c r="C134" s="2">
-        <v>9822</v>
+        <v>2499</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E134" s="3">
-        <v>58.3</v>
+        <v>6.2</v>
       </c>
       <c r="F134" s="3">
-        <v>98.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G134" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F134-E134</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H134" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F134&gt;50, G134*0.2, G134*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>16</v>
@@ -10718,36 +11210,36 @@
     </row>
     <row r="135" spans="1:11" ht="15.6">
       <c r="A135" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B135" s="4">
-        <v>1134</v>
+        <v>1070</v>
       </c>
       <c r="C135" s="2">
-        <v>9822</v>
+        <v>2499</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E135" s="3">
-        <v>58.3</v>
+        <v>6.2</v>
       </c>
       <c r="F135" s="3">
-        <v>98.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G135" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F135-E135</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H135" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F135&gt;50, G135*0.2, G135*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>16</v>
@@ -10755,104 +11247,104 @@
     </row>
     <row r="136" spans="1:11" ht="15.6">
       <c r="A136" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B136" s="4">
-        <v>1135</v>
+        <v>1095</v>
       </c>
       <c r="C136" s="2">
-        <v>8722</v>
+        <v>2499</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E136" s="3">
-        <v>344</v>
+        <v>6.2</v>
       </c>
       <c r="F136" s="3">
-        <v>502</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G136" s="3">
-        <f t="shared" si="8"/>
-        <v>158</v>
+        <f>F136-E136</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H136" s="3">
-        <f t="shared" si="9"/>
-        <v>31.6</v>
+        <f>IF(F136&gt;50, G136*0.2, G136*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="15.6">
       <c r="A137" s="5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B137" s="4">
-        <v>1136</v>
+        <v>1029</v>
       </c>
       <c r="C137" s="2">
-        <v>2242</v>
+        <v>2499</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E137" s="3">
-        <v>60</v>
+        <v>6.2</v>
       </c>
       <c r="F137" s="3">
-        <v>124</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G137" s="3">
-        <f t="shared" si="8"/>
-        <v>64</v>
+        <f>F137-E137</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H137" s="3">
-        <f t="shared" si="9"/>
-        <v>12.8</v>
+        <f>IF(F137&gt;50, G137*0.2, G137*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="15.6">
       <c r="A138" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B138" s="4">
-        <v>1137</v>
+        <v>1036</v>
       </c>
       <c r="C138" s="2">
-        <v>9822</v>
+        <v>2499</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E138" s="3">
-        <v>58.3</v>
+        <v>6.2</v>
       </c>
       <c r="F138" s="3">
-        <v>98.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G138" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F138-E138</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H138" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F138&gt;50, G138*0.2, G138*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>2</v>
@@ -10861,78 +11353,78 @@
         <v>1</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="15.6">
       <c r="A139" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B139" s="4">
-        <v>1138</v>
+        <v>1038</v>
       </c>
       <c r="C139" s="2">
-        <v>8722</v>
+        <v>2499</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E139" s="3">
-        <v>344</v>
+        <v>6.2</v>
       </c>
       <c r="F139" s="3">
-        <v>502</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G139" s="3">
-        <f t="shared" si="8"/>
-        <v>158</v>
+        <f>F139-E139</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H139" s="3">
-        <f t="shared" si="9"/>
-        <v>31.6</v>
+        <f>IF(F139&gt;50, G139*0.2, G139*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="15.6">
       <c r="A140" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B140" s="4">
-        <v>1139</v>
+        <v>1057</v>
       </c>
       <c r="C140" s="2">
-        <v>4421</v>
+        <v>2499</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E140" s="3">
-        <v>45</v>
+        <v>6.2</v>
       </c>
       <c r="F140" s="3">
-        <v>87</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G140" s="3">
-        <f t="shared" si="8"/>
-        <v>42</v>
+        <f>F140-E140</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H140" s="3">
-        <f t="shared" si="9"/>
-        <v>8.4</v>
+        <f>IF(F140&gt;50, G140*0.2, G140*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>5</v>
@@ -10940,30 +11432,30 @@
     </row>
     <row r="141" spans="1:11" ht="15.6">
       <c r="A141" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B141" s="4">
-        <v>1140</v>
+        <v>1105</v>
       </c>
       <c r="C141" s="2">
-        <v>4421</v>
+        <v>2499</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E141" s="3">
-        <v>45</v>
+        <v>6.2</v>
       </c>
       <c r="F141" s="3">
-        <v>87</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="G141" s="3">
-        <f t="shared" si="8"/>
-        <v>42</v>
+        <f>F141-E141</f>
+        <v>2.9999999999999991</v>
       </c>
       <c r="H141" s="3">
-        <f t="shared" si="9"/>
-        <v>8.4</v>
+        <f>IF(F141&gt;50, G141*0.2, G141*0.1)</f>
+        <v>0.29999999999999993</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>2</v>
@@ -10972,15 +11464,15 @@
         <v>1</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="15.6">
       <c r="A142" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B142" s="4">
-        <v>1141</v>
+        <v>1162</v>
       </c>
       <c r="C142" s="2">
         <v>9212</v>
@@ -10995,18 +11487,18 @@
         <v>7</v>
       </c>
       <c r="G142" s="3">
-        <f t="shared" si="8"/>
+        <f>F142-E142</f>
         <v>3</v>
       </c>
       <c r="H142" s="3">
-        <f t="shared" si="9"/>
+        <f>IF(F142&gt;50, G142*0.2, G142*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>16</v>
@@ -11014,39 +11506,39 @@
     </row>
     <row r="143" spans="1:11" ht="15.6">
       <c r="A143" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B143" s="4">
-        <v>1142</v>
+        <v>1126</v>
       </c>
       <c r="C143" s="2">
-        <v>2242</v>
+        <v>9212</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E143" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F143" s="3">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G143" s="3">
-        <f t="shared" si="8"/>
-        <v>64</v>
+        <f>F143-E143</f>
+        <v>3</v>
       </c>
       <c r="H143" s="3">
-        <f t="shared" si="9"/>
-        <v>12.8</v>
+        <f>IF(F143&gt;50, G143*0.2, G143*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="15.6">
@@ -11054,33 +11546,33 @@
         <v>22</v>
       </c>
       <c r="B144" s="4">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="C144" s="2">
-        <v>9822</v>
+        <v>9212</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E144" s="3">
-        <v>58.3</v>
+        <v>4</v>
       </c>
       <c r="F144" s="3">
-        <v>98.4</v>
+        <v>7</v>
       </c>
       <c r="G144" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F144-E144</f>
+        <v>3</v>
       </c>
       <c r="H144" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F144&gt;50, G144*0.2, G144*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>16</v>
@@ -11088,104 +11580,104 @@
     </row>
     <row r="145" spans="1:11" ht="15.6">
       <c r="A145" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B145" s="4">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="C145" s="2">
-        <v>2242</v>
+        <v>9212</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E145" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F145" s="3">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G145" s="3">
-        <f t="shared" si="8"/>
-        <v>64</v>
+        <f>F145-E145</f>
+        <v>3</v>
       </c>
       <c r="H145" s="3">
-        <f t="shared" si="9"/>
-        <v>12.8</v>
+        <f>IF(F145&gt;50, G145*0.2, G145*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="15.6">
       <c r="A146" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B146" s="4">
-        <v>1145</v>
+        <v>1163</v>
       </c>
       <c r="C146" s="2">
-        <v>4421</v>
+        <v>9212</v>
       </c>
       <c r="D146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="3">
+        <v>4</v>
+      </c>
+      <c r="F146" s="3">
+        <v>7</v>
+      </c>
+      <c r="G146" s="3">
+        <f>F146-E146</f>
         <v>3</v>
       </c>
-      <c r="E146" s="3">
-        <v>45</v>
-      </c>
-      <c r="F146" s="3">
-        <v>87</v>
-      </c>
-      <c r="G146" s="3">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
       <c r="H146" s="3">
-        <f t="shared" si="9"/>
-        <v>8.4</v>
+        <f>IF(F146&gt;50, G146*0.2, G146*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="15.6">
       <c r="A147" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B147" s="4">
-        <v>1146</v>
+        <v>1013</v>
       </c>
       <c r="C147" s="2">
-        <v>8722</v>
+        <v>9212</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E147" s="3">
-        <v>344</v>
+        <v>4</v>
       </c>
       <c r="F147" s="3">
-        <v>502</v>
+        <v>7</v>
       </c>
       <c r="G147" s="3">
-        <f t="shared" si="8"/>
-        <v>158</v>
+        <f>F147-E147</f>
+        <v>3</v>
       </c>
       <c r="H147" s="3">
-        <f t="shared" si="9"/>
-        <v>31.6</v>
+        <f>IF(F147&gt;50, G147*0.2, G147*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>19</v>
@@ -11194,52 +11686,52 @@
         <v>18</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="15.6">
       <c r="A148" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B148" s="4">
-        <v>1147</v>
+        <v>1097</v>
       </c>
       <c r="C148" s="2">
-        <v>9822</v>
+        <v>9212</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E148" s="3">
-        <v>58.3</v>
+        <v>4</v>
       </c>
       <c r="F148" s="3">
-        <v>98.4</v>
+        <v>7</v>
       </c>
       <c r="G148" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F148-E148</f>
+        <v>3</v>
       </c>
       <c r="H148" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F148&gt;50, G148*0.2, G148*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="15.6">
       <c r="A149" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B149" s="4">
-        <v>1148</v>
+        <v>1131</v>
       </c>
       <c r="C149" s="2">
         <v>9212</v>
@@ -11254,18 +11746,18 @@
         <v>7</v>
       </c>
       <c r="G149" s="3">
-        <f t="shared" si="8"/>
+        <f>F149-E149</f>
         <v>3</v>
       </c>
       <c r="H149" s="3">
-        <f t="shared" si="9"/>
+        <f>IF(F149&gt;50, G149*0.2, G149*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>16</v>
@@ -11273,73 +11765,73 @@
     </row>
     <row r="150" spans="1:11" ht="15.6">
       <c r="A150" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B150" s="4">
-        <v>1149</v>
+        <v>1132</v>
       </c>
       <c r="C150" s="2">
-        <v>8722</v>
+        <v>9212</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E150" s="3">
-        <v>344</v>
+        <v>4</v>
       </c>
       <c r="F150" s="3">
-        <v>502</v>
+        <v>7</v>
       </c>
       <c r="G150" s="3">
-        <f t="shared" si="8"/>
-        <v>158</v>
+        <f>F150-E150</f>
+        <v>3</v>
       </c>
       <c r="H150" s="3">
-        <f t="shared" si="9"/>
-        <v>31.6</v>
+        <f>IF(F150&gt;50, G150*0.2, G150*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="15.6">
       <c r="A151" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B151" s="4">
-        <v>1150</v>
+        <v>1024</v>
       </c>
       <c r="C151" s="2">
-        <v>2242</v>
+        <v>9212</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E151" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F151" s="3">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G151" s="3">
-        <f t="shared" si="8"/>
-        <v>64</v>
+        <f>F151-E151</f>
+        <v>3</v>
       </c>
       <c r="H151" s="3">
-        <f t="shared" si="9"/>
-        <v>12.8</v>
+        <f>IF(F151&gt;50, G151*0.2, G151*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K151" s="2" t="s">
         <v>8</v>
@@ -11347,30 +11839,30 @@
     </row>
     <row r="152" spans="1:11" ht="15.6">
       <c r="A152" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B152" s="4">
-        <v>1151</v>
+        <v>1141</v>
       </c>
       <c r="C152" s="2">
-        <v>2242</v>
+        <v>9212</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E152" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F152" s="3">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G152" s="3">
-        <f t="shared" si="8"/>
-        <v>64</v>
+        <f>F152-E152</f>
+        <v>3</v>
       </c>
       <c r="H152" s="3">
-        <f t="shared" si="9"/>
-        <v>12.8</v>
+        <f>IF(F152&gt;50, G152*0.2, G152*0.1)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>2</v>
@@ -11379,35 +11871,35 @@
         <v>1</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="15.6">
       <c r="A153" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B153" s="4">
-        <v>1152</v>
+        <v>1071</v>
       </c>
       <c r="C153" s="2">
-        <v>4421</v>
+        <v>1109</v>
       </c>
       <c r="D153" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E153" s="3">
         <v>3</v>
       </c>
-      <c r="E153" s="3">
-        <v>45</v>
-      </c>
       <c r="F153" s="3">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="G153" s="3">
-        <f t="shared" si="8"/>
-        <v>42</v>
+        <f>F153-E153</f>
+        <v>5</v>
       </c>
       <c r="H153" s="3">
-        <f t="shared" si="9"/>
-        <v>8.4</v>
+        <f>IF(F153&gt;50, G153*0.2, G153*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I153" s="2" t="s">
         <v>7</v>
@@ -11416,78 +11908,78 @@
         <v>6</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="15.6">
       <c r="A154" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B154" s="4">
-        <v>1153</v>
+        <v>1082</v>
       </c>
       <c r="C154" s="2">
-        <v>8722</v>
+        <v>1109</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E154" s="3">
-        <v>344</v>
+        <v>3</v>
       </c>
       <c r="F154" s="3">
-        <v>502</v>
+        <v>8</v>
       </c>
       <c r="G154" s="3">
-        <f t="shared" si="8"/>
-        <v>158</v>
+        <f>F154-E154</f>
+        <v>5</v>
       </c>
       <c r="H154" s="3">
-        <f t="shared" si="9"/>
-        <v>31.6</v>
+        <f>IF(F154&gt;50, G154*0.2, G154*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="15.6">
       <c r="A155" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B155" s="4">
-        <v>1154</v>
+        <v>1083</v>
       </c>
       <c r="C155" s="2">
-        <v>9822</v>
+        <v>1109</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E155" s="3">
-        <v>58.3</v>
+        <v>3</v>
       </c>
       <c r="F155" s="3">
-        <v>98.4</v>
+        <v>8</v>
       </c>
       <c r="G155" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F155-E155</f>
+        <v>5</v>
       </c>
       <c r="H155" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F155&gt;50, G155*0.2, G155*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>0</v>
@@ -11495,30 +11987,30 @@
     </row>
     <row r="156" spans="1:11" ht="15.6">
       <c r="A156" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B156" s="4">
-        <v>1155</v>
+        <v>1005</v>
       </c>
       <c r="C156" s="2">
-        <v>4421</v>
+        <v>1109</v>
       </c>
       <c r="D156" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E156" s="3">
         <v>3</v>
       </c>
-      <c r="E156" s="3">
-        <v>45</v>
-      </c>
       <c r="F156" s="3">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="G156" s="3">
-        <f t="shared" si="8"/>
-        <v>42</v>
+        <f>F156-E156</f>
+        <v>5</v>
       </c>
       <c r="H156" s="3">
-        <f t="shared" si="9"/>
-        <v>8.4</v>
+        <f>IF(F156&gt;50, G156*0.2, G156*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I156" s="2" t="s">
         <v>10</v>
@@ -11532,30 +12024,30 @@
     </row>
     <row r="157" spans="1:11" ht="15.6">
       <c r="A157" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B157" s="4">
-        <v>1156</v>
+        <v>1009</v>
       </c>
       <c r="C157" s="2">
-        <v>2242</v>
+        <v>1109</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E157" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F157" s="3">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="G157" s="3">
-        <f t="shared" si="8"/>
-        <v>64</v>
+        <f>F157-E157</f>
+        <v>5</v>
       </c>
       <c r="H157" s="3">
-        <f t="shared" si="9"/>
-        <v>12.8</v>
+        <f>IF(F157&gt;50, G157*0.2, G157*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>10</v>
@@ -11564,35 +12056,35 @@
         <v>9</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="15.6">
       <c r="A158" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B158" s="4">
-        <v>1157</v>
+        <v>1018</v>
       </c>
       <c r="C158" s="2">
-        <v>9212</v>
+        <v>1109</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E158" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F158" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G158" s="3">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f>F158-E158</f>
+        <v>5</v>
       </c>
       <c r="H158" s="3">
-        <f t="shared" si="9"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F158&gt;50, G158*0.2, G158*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I158" s="2" t="s">
         <v>10</v>
@@ -11601,72 +12093,72 @@
         <v>9</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="15.6">
       <c r="A159" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B159" s="4">
-        <v>1158</v>
+        <v>1056</v>
       </c>
       <c r="C159" s="2">
-        <v>8722</v>
+        <v>1109</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E159" s="3">
-        <v>344</v>
+        <v>3</v>
       </c>
       <c r="F159" s="3">
-        <v>502</v>
+        <v>8</v>
       </c>
       <c r="G159" s="3">
-        <f t="shared" si="8"/>
-        <v>158</v>
+        <f>F159-E159</f>
+        <v>5</v>
       </c>
       <c r="H159" s="3">
-        <f t="shared" si="9"/>
-        <v>31.6</v>
+        <f>IF(F159&gt;50, G159*0.2, G159*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="15.6">
       <c r="A160" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B160" s="4">
-        <v>1159</v>
+        <v>1061</v>
       </c>
       <c r="C160" s="2">
-        <v>6622</v>
+        <v>1109</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E160" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F160" s="3">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="G160" s="3">
-        <f t="shared" si="8"/>
-        <v>35</v>
+        <f>F160-E160</f>
+        <v>5</v>
       </c>
       <c r="H160" s="3">
-        <f t="shared" si="9"/>
-        <v>7</v>
+        <f>IF(F160&gt;50, G160*0.2, G160*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I160" s="2" t="s">
         <v>10</v>
@@ -11675,300 +12167,300 @@
         <v>9</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="15.6">
       <c r="A161" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B161" s="4">
-        <v>1160</v>
+        <v>1063</v>
       </c>
       <c r="C161" s="2">
-        <v>9822</v>
+        <v>1109</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E161" s="3">
-        <v>58.3</v>
+        <v>3</v>
       </c>
       <c r="F161" s="3">
-        <v>98.4</v>
+        <v>8</v>
       </c>
       <c r="G161" s="3">
-        <f t="shared" si="8"/>
-        <v>40.100000000000009</v>
+        <f>F161-E161</f>
+        <v>5</v>
       </c>
       <c r="H161" s="3">
-        <f t="shared" si="9"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F161&gt;50, G161*0.2, G161*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="15.6">
       <c r="A162" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B162" s="4">
-        <v>1161</v>
+        <v>1069</v>
       </c>
       <c r="C162" s="2">
-        <v>4421</v>
+        <v>1109</v>
       </c>
       <c r="D162" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E162" s="3">
         <v>3</v>
       </c>
-      <c r="E162" s="3">
-        <v>45</v>
-      </c>
       <c r="F162" s="3">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="G162" s="3">
-        <f t="shared" ref="G162:G172" si="10">F162-E162</f>
-        <v>42</v>
+        <f>F162-E162</f>
+        <v>5</v>
       </c>
       <c r="H162" s="3">
-        <f t="shared" ref="H162:H172" si="11">IF(F162&gt;50, G162*0.2, G162*0.1)</f>
-        <v>8.4</v>
+        <f>IF(F162&gt;50, G162*0.2, G162*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="15.6">
       <c r="A163" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B163" s="4">
-        <v>1162</v>
+        <v>1072</v>
       </c>
       <c r="C163" s="2">
-        <v>9212</v>
+        <v>1109</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E163" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F163" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G163" s="3">
-        <f t="shared" si="10"/>
-        <v>3</v>
+        <f>F163-E163</f>
+        <v>5</v>
       </c>
       <c r="H163" s="3">
-        <f t="shared" si="11"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F163&gt;50, G163*0.2, G163*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="15.6">
       <c r="A164" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B164" s="4">
-        <v>1163</v>
+        <v>1007</v>
       </c>
       <c r="C164" s="2">
-        <v>9212</v>
+        <v>1109</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E164" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F164" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G164" s="3">
-        <f t="shared" si="10"/>
-        <v>3</v>
+        <f>F164-E164</f>
+        <v>5</v>
       </c>
       <c r="H164" s="3">
-        <f t="shared" si="11"/>
-        <v>0.30000000000000004</v>
+        <f>IF(F164&gt;50, G164*0.2, G164*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="15.6">
       <c r="A165" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B165" s="4">
-        <v>1164</v>
+        <v>1023</v>
       </c>
       <c r="C165" s="2">
-        <v>9822</v>
+        <v>1109</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E165" s="3">
-        <v>58.3</v>
+        <v>3</v>
       </c>
       <c r="F165" s="3">
-        <v>98.4</v>
+        <v>8</v>
       </c>
       <c r="G165" s="3">
-        <f t="shared" si="10"/>
-        <v>40.100000000000009</v>
+        <f>F165-E165</f>
+        <v>5</v>
       </c>
       <c r="H165" s="3">
-        <f t="shared" si="11"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F165&gt;50, G165*0.2, G165*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="15.6">
       <c r="A166" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B166" s="4">
-        <v>1165</v>
+        <v>1075</v>
       </c>
       <c r="C166" s="2">
-        <v>9822</v>
+        <v>1109</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E166" s="3">
-        <v>58.3</v>
+        <v>3</v>
       </c>
       <c r="F166" s="3">
-        <v>98.4</v>
+        <v>8</v>
       </c>
       <c r="G166" s="3">
-        <f t="shared" si="10"/>
-        <v>40.100000000000009</v>
+        <f>F166-E166</f>
+        <v>5</v>
       </c>
       <c r="H166" s="3">
-        <f t="shared" si="11"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F166&gt;50, G166*0.2, G166*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="15.6">
       <c r="A167" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B167" s="4">
-        <v>1166</v>
+        <v>1086</v>
       </c>
       <c r="C167" s="2">
-        <v>8722</v>
+        <v>1109</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E167" s="3">
-        <v>344</v>
+        <v>3</v>
       </c>
       <c r="F167" s="3">
-        <v>502</v>
+        <v>8</v>
       </c>
       <c r="G167" s="3">
-        <f t="shared" si="10"/>
-        <v>158</v>
+        <f>F167-E167</f>
+        <v>5</v>
       </c>
       <c r="H167" s="3">
-        <f t="shared" si="11"/>
-        <v>31.6</v>
+        <f>IF(F167&gt;50, G167*0.2, G167*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="15.6">
       <c r="A168" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B168" s="4">
-        <v>1167</v>
+        <v>1107</v>
       </c>
       <c r="C168" s="2">
-        <v>2242</v>
+        <v>1109</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E168" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F168" s="3">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="G168" s="3">
-        <f t="shared" si="10"/>
-        <v>64</v>
+        <f>F168-E168</f>
+        <v>5</v>
       </c>
       <c r="H168" s="3">
-        <f t="shared" si="11"/>
-        <v>12.8</v>
+        <f>IF(F168&gt;50, G168*0.2, G168*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K168" s="2" t="s">
         <v>13</v>
@@ -11976,141 +12468,141 @@
     </row>
     <row r="169" spans="1:11" ht="15.6">
       <c r="A169" s="5" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B169" s="4">
-        <v>1168</v>
+        <v>1021</v>
       </c>
       <c r="C169" s="2">
-        <v>9822</v>
+        <v>1109</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E169" s="3">
-        <v>58.3</v>
+        <v>3</v>
       </c>
       <c r="F169" s="3">
-        <v>98.4</v>
+        <v>8</v>
       </c>
       <c r="G169" s="3">
-        <f t="shared" si="10"/>
-        <v>40.100000000000009</v>
+        <f>F169-E169</f>
+        <v>5</v>
       </c>
       <c r="H169" s="3">
-        <f t="shared" si="11"/>
-        <v>8.0200000000000014</v>
+        <f>IF(F169&gt;50, G169*0.2, G169*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="15.6">
       <c r="A170" s="5" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B170" s="4">
-        <v>1169</v>
+        <v>1031</v>
       </c>
       <c r="C170" s="2">
-        <v>8722</v>
+        <v>1109</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E170" s="3">
-        <v>344</v>
+        <v>3</v>
       </c>
       <c r="F170" s="3">
-        <v>502</v>
+        <v>8</v>
       </c>
       <c r="G170" s="3">
-        <f t="shared" si="10"/>
-        <v>158</v>
+        <f>F170-E170</f>
+        <v>5</v>
       </c>
       <c r="H170" s="3">
-        <f t="shared" si="11"/>
-        <v>31.6</v>
+        <f>IF(F170&gt;50, G170*0.2, G170*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="15.6">
       <c r="A171" s="5" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B171" s="4">
-        <v>1170</v>
+        <v>1040</v>
       </c>
       <c r="C171" s="2">
-        <v>4421</v>
+        <v>1109</v>
       </c>
       <c r="D171" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E171" s="3">
         <v>3</v>
       </c>
-      <c r="E171" s="3">
-        <v>45</v>
-      </c>
       <c r="F171" s="3">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="G171" s="3">
-        <f t="shared" si="10"/>
-        <v>42</v>
+        <f>F171-E171</f>
+        <v>5</v>
       </c>
       <c r="H171" s="3">
-        <f t="shared" si="11"/>
-        <v>8.4</v>
+        <f>IF(F171&gt;50, G171*0.2, G171*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="15.6">
       <c r="A172" s="5" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B172" s="4">
-        <v>1171</v>
+        <v>1076</v>
       </c>
       <c r="C172" s="2">
-        <v>4421</v>
+        <v>1109</v>
       </c>
       <c r="D172" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E172" s="3">
         <v>3</v>
       </c>
-      <c r="E172" s="3">
-        <v>45</v>
-      </c>
       <c r="F172" s="3">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="G172" s="3">
-        <f t="shared" si="10"/>
-        <v>42</v>
+        <f>F172-E172</f>
+        <v>5</v>
       </c>
       <c r="H172" s="3">
-        <f t="shared" si="11"/>
-        <v>8.4</v>
+        <f>IF(F172&gt;50, G172*0.2, G172*0.1)</f>
+        <v>0.5</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>2</v>
@@ -12119,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -12128,7 +12620,7 @@
       </c>
       <c r="F176" s="1">
         <f>SUM(F2:F172)</f>
-        <v>17110.599999999995</v>
+        <v>17110.599999999991</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -12137,7 +12629,7 @@
       </c>
       <c r="F177" s="1">
         <f>SUMIF(F2:F172,"&gt;50")</f>
-        <v>16088.399999999994</v>
+        <v>16088.399999999992</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -12146,18 +12638,18 @@
       </c>
       <c r="F178" s="1">
         <f>SUMIF(F2:F172, "&lt;=50")</f>
-        <v>1022.1999999999997</v>
+        <v>1022.2000000000011</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K172" xr:uid="{033C8F26-51CB-4359-B9FF-5D995B113350}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K106">
-      <sortCondition ref="J1:J172"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:K172" xr:uid="{033C8F26-51CB-4359-B9FF-5D995B113350}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K172">
     <sortCondition ref="B2:B172"/>
   </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="U11:V11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="17" orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
